--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -66,7 +66,7 @@
     <x:t>Amateur</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA  ABASTAS AMANTE</x:t>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
   </x:si>
   <x:si>
     <x:t>Manimpis, City Of San Fernando (Capital), Pampanga</x:t>
@@ -156,7 +156,7 @@
     <x:t>61-6-2025-1054</x:t>
   </x:si>
   <x:si>
-    <x:t>ANGELICA  VERGARA PANCHITO</x:t>
+    <x:t>ANGELICA VERGARA PANCHITO</x:t>
   </x:si>
   <x:si>
     <x:t>TEMP-ROIII-1007-25</x:t>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="June 2025" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
-  <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+  <x:si>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -253,7 +217,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -280,12 +244,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -293,6 +251,27 @@
       <x:sz val="11.0"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -307,13 +286,6 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -358,12 +330,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -375,14 +347,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -564,7 +536,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -575,183 +547,201 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1015,741 +1005,717 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
-    </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="C6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="D6" s="12" t="s"/>
+      <x:c r="E6" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E5" s="10" t="s">
+      <x:c r="F6" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5" s="10" t="s">
+      <x:c r="G6" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="s">
+      <x:c r="H6" s="13">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L6" s="15">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="s">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I5" s="10" t="s">
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J5" s="10" t="s">
+      <x:c r="F7" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K5" s="10" t="s">
+      <x:c r="G7" s="16" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L5" s="10" t="s">
+      <x:c r="H7" s="17">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I7" s="17">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L7" s="17">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M7" s="16" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="s">
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="19" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s"/>
+      <x:c r="E8" s="19" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="11" t="s">
+      <x:c r="G8" s="19" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="s">
+      <x:c r="H8" s="20">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I8" s="20">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J8" s="19" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K8" s="21" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="20">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="19" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="s"/>
-      <x:c r="E6" s="11" t="s">
+      <x:c r="C9" s="19" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
+      <x:c r="D9" s="19" t="s"/>
+      <x:c r="E9" s="19" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="s">
+      <x:c r="F9" s="19" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H6" s="12">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I6" s="12">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="G9" s="19" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H9" s="20">
+        <x:v>45827.2931018519</x:v>
+      </x:c>
+      <x:c r="I9" s="20">
+        <x:v>45827.293125</x:v>
+      </x:c>
+      <x:c r="J9" s="19" t="n">
+        <x:v>1435677</x:v>
+      </x:c>
+      <x:c r="K9" s="21" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L9" s="20">
+        <x:v>45827.2985763889</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s"/>
+      <x:c r="E10" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>45825.2509606481</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>45825.2509837963</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>2744256</x:v>
+      </x:c>
+      <x:c r="K10" s="14" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L10" s="15">
+        <x:v>45825.8750462963</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I11" s="22">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K11" s="14" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L11" s="15">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="s"/>
+      <x:c r="E12" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I12" s="13">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K12" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L6" s="12">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
-    </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="L12" s="15">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M12" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="s"/>
+      <x:c r="E13" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I13" s="13">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K13" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L13" s="15">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M13" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="s"/>
+      <x:c r="E14" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I14" s="13">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K14" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L14" s="15">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M14" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="s"/>
+      <x:c r="E15" s="11" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I15" s="13">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="15">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M15" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="11" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s"/>
-      <x:c r="E7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I7" s="12">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="E16" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I16" s="13">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K16" s="14" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L16" s="15">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M16" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L7" s="12">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
-    </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B8" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H17" s="13">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I17" s="13">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L17" s="15">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M17" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="D18" s="12" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H8" s="16">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I8" s="16">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J8" s="15" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K8" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L8" s="18">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C9" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F9" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G9" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K9" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L9" s="18">
-        <x:v>45827.2985763889</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45825.2509606481</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>2744256</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45825.8750462963</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I11" s="19">
+      <x:c r="E18" s="11" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I18" s="22">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s"/>
-      <x:c r="E14" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
+      <x:c r="J18" s="12" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K18" s="14" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="15">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M18" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="11" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s"/>
-      <x:c r="E15" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="C19" s="11" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="D19" s="12" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
+      <x:c r="F19" s="11" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G19" s="11" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I18" s="19">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
+      <x:c r="H19" s="13">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I19" s="19">
+      <x:c r="I19" s="22">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
+      <x:c r="J19" s="12" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="K19" s="14" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L19" s="18">
+      <x:c r="L19" s="15">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>18</x:v>
+      <x:c r="M19" s="11" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="20" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C22" s="21" t="s"/>
-      <x:c r="D22" s="21" t="s"/>
-      <x:c r="E22" s="22" t="s"/>
-      <x:c r="F22" s="22" t="s"/>
+      <x:c r="B22" s="23" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C22" s="24" t="s"/>
+      <x:c r="D22" s="24" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="25" t="s"/>
     </x:row>
     <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C23" s="24" t="s"/>
-      <x:c r="D23" s="24" t="s"/>
-      <x:c r="E23" s="24" t="s"/>
-      <x:c r="F23" s="25" t="s">
-        <x:v>72</x:v>
+      <x:c r="B23" s="26" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="B24" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="B25" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s"/>
+      <x:c r="D25" s="30" t="s"/>
+      <x:c r="E25" s="30" t="s"/>
+      <x:c r="F25" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="B26" s="29" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s"/>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="30" t="s"/>
+      <x:c r="F26" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="B27" s="29" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="B28" s="29" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s"/>
+      <x:c r="D28" s="30" t="s"/>
+      <x:c r="E28" s="30" t="s"/>
+      <x:c r="F28" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+      <x:c r="B29" s="29" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s"/>
+      <x:c r="D29" s="30" t="s"/>
+      <x:c r="E29" s="30" t="s"/>
+      <x:c r="F29" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="29" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s"/>
+      <x:c r="D30" s="30" t="s"/>
+      <x:c r="E30" s="30" t="s"/>
+      <x:c r="F30" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s"/>
+      <x:c r="D31" s="30" t="s"/>
+      <x:c r="E31" s="30" t="s"/>
+      <x:c r="F31" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C32" s="30" t="s"/>
+      <x:c r="D32" s="30" t="s"/>
+      <x:c r="E32" s="30" t="s"/>
+      <x:c r="F32" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B33" s="29" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C33" s="30" t="s"/>
-      <x:c r="D33" s="30" t="s"/>
-      <x:c r="E33" s="30" t="s"/>
-      <x:c r="F33" s="31" t="n">
+      <x:c r="B33" s="32" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C33" s="33" t="s"/>
+      <x:c r="D33" s="33" t="s"/>
+      <x:c r="E33" s="33" t="s"/>
+      <x:c r="F33" s="34" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -1007,7 +1007,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>45809</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -1589,62 +1589,42 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="23" t="s">
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="23" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C22" s="24" t="s"/>
-      <x:c r="D22" s="24" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="25" t="s"/>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="C24" s="24" t="s"/>
+      <x:c r="D24" s="24" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="25" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="26" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="s">
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="s">
         <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="29" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C25" s="30" t="s"/>
-      <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="30" t="s"/>
-      <x:c r="F25" s="31" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="29" t="s">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="30" t="s"/>
       <x:c r="D26" s="30" t="s"/>
       <x:c r="E26" s="30" t="s"/>
       <x:c r="F26" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="29" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="30" t="s"/>
       <x:c r="D27" s="30" t="s"/>
@@ -1655,18 +1635,18 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
       <x:c r="B28" s="29" t="s">
-        <x:v>28</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C28" s="30" t="s"/>
       <x:c r="D28" s="30" t="s"/>
       <x:c r="E28" s="30" t="s"/>
       <x:c r="F28" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="29" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C29" s="30" t="s"/>
       <x:c r="D29" s="30" t="s"/>
@@ -1677,18 +1657,18 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="29" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C30" s="30" t="s"/>
       <x:c r="D30" s="30" t="s"/>
       <x:c r="E30" s="30" t="s"/>
       <x:c r="F30" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="29" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C31" s="30" t="s"/>
       <x:c r="D31" s="30" t="s"/>
@@ -1699,28 +1679,48 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="29" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C32" s="30" t="s"/>
       <x:c r="D32" s="30" t="s"/>
       <x:c r="E32" s="30" t="s"/>
       <x:c r="F32" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="29" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s"/>
+      <x:c r="D33" s="30" t="s"/>
+      <x:c r="E33" s="30" t="s"/>
+      <x:c r="F33" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="29" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B33" s="32" t="s">
+    <x:row r="35" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B35" s="32" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C33" s="33" t="s"/>
-      <x:c r="D33" s="33" t="s"/>
-      <x:c r="E33" s="33" t="s"/>
-      <x:c r="F33" s="34" t="n">
+      <x:c r="C35" s="33" t="s"/>
+      <x:c r="D35" s="33" t="s"/>
+      <x:c r="E35" s="33" t="s"/>
+      <x:c r="F35" s="34" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2680,12 +2680,11 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="14">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
+  <x:mergeCells count="15">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B24:F24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
@@ -2695,6 +2694,8 @@
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -614,7 +614,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -650,6 +650,50 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -669,32 +713,12 @@
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1068,7 +1092,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -1106,7 +1130,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>
@@ -1218,506 +1242,532 @@
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="11" t="s">
+      <x:c r="B10" s="22" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="s">
+      <x:c r="C10" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="s"/>
-      <x:c r="E10" s="11" t="s">
+      <x:c r="D10" s="23" t="s"/>
+      <x:c r="E10" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="s">
+      <x:c r="F10" s="22" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G10" s="11" t="s">
+      <x:c r="G10" s="22" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H10" s="13">
+      <x:c r="H10" s="24">
         <x:v>45825.2509606481</x:v>
       </x:c>
-      <x:c r="I10" s="13">
+      <x:c r="I10" s="24">
         <x:v>45825.2509837963</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="n">
+      <x:c r="J10" s="23" t="n">
         <x:v>2744256</x:v>
       </x:c>
-      <x:c r="K10" s="14" t="n">
+      <x:c r="K10" s="25" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L10" s="15">
+      <x:c r="L10" s="26">
         <x:v>45825.8750462963</x:v>
       </x:c>
-      <x:c r="M10" s="11" t="s">
+      <x:c r="M10" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="11" t="s">
+      <x:c r="B11" s="22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="s">
+      <x:c r="C11" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="s">
+      <x:c r="D11" s="23" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E11" s="11" t="s">
+      <x:c r="E11" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="s">
+      <x:c r="F11" s="22" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G11" s="11" t="s">
+      <x:c r="G11" s="22" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H11" s="13">
+      <x:c r="H11" s="24">
         <x:v>45826.1308796296</x:v>
       </x:c>
-      <x:c r="I11" s="22">
+      <x:c r="I11" s="27">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="n">
+      <x:c r="J11" s="23" t="n">
         <x:v>2734401</x:v>
       </x:c>
-      <x:c r="K11" s="14" t="n">
+      <x:c r="K11" s="25" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="L11" s="15">
+      <x:c r="L11" s="26">
         <x:v>45826.1478935185</x:v>
       </x:c>
-      <x:c r="M11" s="11" t="s">
+      <x:c r="M11" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="11" t="s">
+      <x:c r="B12" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="s">
+      <x:c r="C12" s="22" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="s"/>
-      <x:c r="E12" s="11" t="s">
+      <x:c r="D12" s="23" t="s"/>
+      <x:c r="E12" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F12" s="11" t="s">
+      <x:c r="F12" s="22" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G12" s="11" t="s">
+      <x:c r="G12" s="22" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H12" s="13">
+      <x:c r="H12" s="24">
         <x:v>45827.2810416667</x:v>
       </x:c>
-      <x:c r="I12" s="13">
+      <x:c r="I12" s="24">
         <x:v>45827.2810648148</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="n">
+      <x:c r="J12" s="23" t="n">
         <x:v>1616</x:v>
       </x:c>
-      <x:c r="K12" s="14" t="n">
+      <x:c r="K12" s="25" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L12" s="15">
+      <x:c r="L12" s="26">
         <x:v>45827.2917592593</x:v>
       </x:c>
-      <x:c r="M12" s="11" t="s">
+      <x:c r="M12" s="22" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="11" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="s">
+      <x:c r="C13" s="22" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="s"/>
-      <x:c r="E13" s="11" t="s">
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F13" s="11" t="s">
+      <x:c r="F13" s="22" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G13" s="11" t="s">
+      <x:c r="G13" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H13" s="13">
+      <x:c r="H13" s="24">
         <x:v>45825.2634953704</x:v>
       </x:c>
-      <x:c r="I13" s="13">
+      <x:c r="I13" s="24">
         <x:v>45825.2635300926</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="n">
+      <x:c r="J13" s="23" t="n">
         <x:v>274001</x:v>
       </x:c>
-      <x:c r="K13" s="14" t="n">
+      <x:c r="K13" s="25" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L13" s="15">
+      <x:c r="L13" s="26">
         <x:v>45825.2871759259</x:v>
       </x:c>
-      <x:c r="M13" s="11" t="s">
+      <x:c r="M13" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="11" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="s">
+      <x:c r="C14" s="22" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="s"/>
-      <x:c r="E14" s="11" t="s">
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="22" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F14" s="11" t="s">
+      <x:c r="F14" s="22" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G14" s="11" t="s">
+      <x:c r="G14" s="22" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H14" s="13">
+      <x:c r="H14" s="24">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I14" s="13">
+      <x:c r="I14" s="24">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="n">
+      <x:c r="J14" s="23" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K14" s="14" t="n">
+      <x:c r="K14" s="25" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L14" s="15">
+      <x:c r="L14" s="26">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M14" s="11" t="s">
+      <x:c r="M14" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="11" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="s">
+      <x:c r="C15" s="22" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="s"/>
-      <x:c r="E15" s="11" t="s">
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="22" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F15" s="11" t="s">
+      <x:c r="F15" s="22" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G15" s="11" t="s">
+      <x:c r="G15" s="22" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H15" s="13">
+      <x:c r="H15" s="24">
         <x:v>45825.5009259259</x:v>
       </x:c>
-      <x:c r="I15" s="13">
+      <x:c r="I15" s="24">
         <x:v>45825.5010185185</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="n">
+      <x:c r="J15" s="23" t="n">
         <x:v>1434267</x:v>
       </x:c>
-      <x:c r="K15" s="14" t="n">
+      <x:c r="K15" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="15">
+      <x:c r="L15" s="26">
         <x:v>45827.2850694444</x:v>
       </x:c>
-      <x:c r="M15" s="11" t="s">
+      <x:c r="M15" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="11" t="s">
+      <x:c r="B16" s="22" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="s">
+      <x:c r="C16" s="22" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="s">
+      <x:c r="D16" s="23" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E16" s="11" t="s">
+      <x:c r="E16" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F16" s="11" t="s">
+      <x:c r="F16" s="22" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G16" s="11" t="s">
+      <x:c r="G16" s="22" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H16" s="13">
+      <x:c r="H16" s="24">
         <x:v>45825.1485185185</x:v>
       </x:c>
-      <x:c r="I16" s="13">
+      <x:c r="I16" s="24">
         <x:v>45825.1485416667</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="n">
+      <x:c r="J16" s="23" t="n">
         <x:v>15135861</x:v>
       </x:c>
-      <x:c r="K16" s="14" t="n">
+      <x:c r="K16" s="25" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="L16" s="15">
+      <x:c r="L16" s="26">
         <x:v>45825.1676388889</x:v>
       </x:c>
-      <x:c r="M16" s="11" t="s">
+      <x:c r="M16" s="22" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="11" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="s">
+      <x:c r="C17" s="22" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="s">
+      <x:c r="D17" s="23" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E17" s="11" t="s">
+      <x:c r="E17" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F17" s="11" t="s">
+      <x:c r="F17" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G17" s="11" t="s">
+      <x:c r="G17" s="22" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H17" s="13">
+      <x:c r="H17" s="24">
         <x:v>45827.0419791667</x:v>
       </x:c>
-      <x:c r="I17" s="13">
+      <x:c r="I17" s="24">
         <x:v>45827.0420138889</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="n">
+      <x:c r="J17" s="23" t="n">
         <x:v>52268</x:v>
       </x:c>
-      <x:c r="K17" s="14" t="n">
+      <x:c r="K17" s="25" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L17" s="15">
+      <x:c r="L17" s="26">
         <x:v>45827.0460069444</x:v>
       </x:c>
-      <x:c r="M17" s="11" t="s">
+      <x:c r="M17" s="22" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="11" t="s">
+      <x:c r="B18" s="22" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="s">
+      <x:c r="C18" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="s">
+      <x:c r="D18" s="23" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E18" s="11" t="s">
+      <x:c r="E18" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F18" s="11" t="s">
+      <x:c r="F18" s="22" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G18" s="11" t="s">
+      <x:c r="G18" s="22" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H18" s="13">
+      <x:c r="H18" s="24">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I18" s="22">
+      <x:c r="I18" s="27">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="n">
+      <x:c r="J18" s="23" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K18" s="14" t="n">
+      <x:c r="K18" s="25" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L18" s="15">
+      <x:c r="L18" s="26">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M18" s="11" t="s">
+      <x:c r="M18" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="11" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="s">
+      <x:c r="C19" s="22" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="s">
+      <x:c r="D19" s="23" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="E19" s="11" t="s">
+      <x:c r="E19" s="22" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F19" s="11" t="s">
+      <x:c r="F19" s="22" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G19" s="11" t="s">
+      <x:c r="G19" s="22" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H19" s="13">
+      <x:c r="H19" s="24">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I19" s="22">
+      <x:c r="I19" s="27">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="n">
+      <x:c r="J19" s="23" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K19" s="14" t="n">
+      <x:c r="K19" s="25" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L19" s="15">
+      <x:c r="L19" s="26">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M19" s="11" t="s">
+      <x:c r="M19" s="22" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B20" s="28" t="s"/>
+      <x:c r="C20" s="28" t="s"/>
+      <x:c r="D20" s="28" t="s"/>
+      <x:c r="E20" s="28" t="s"/>
+      <x:c r="F20" s="28" t="s"/>
+      <x:c r="G20" s="28" t="s"/>
+      <x:c r="H20" s="28" t="s"/>
+      <x:c r="I20" s="28" t="s"/>
+      <x:c r="J20" s="28" t="s"/>
+      <x:c r="K20" s="28" t="s"/>
+      <x:c r="L20" s="28" t="s"/>
+      <x:c r="M20" s="28" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B21" s="28" t="s"/>
+      <x:c r="C21" s="28" t="s"/>
+      <x:c r="D21" s="28" t="s"/>
+      <x:c r="E21" s="28" t="s"/>
+      <x:c r="F21" s="28" t="s"/>
+      <x:c r="G21" s="28" t="s"/>
+      <x:c r="H21" s="28" t="s"/>
+      <x:c r="I21" s="28" t="s"/>
+      <x:c r="J21" s="28" t="s"/>
+      <x:c r="K21" s="28" t="s"/>
+      <x:c r="L21" s="28" t="s"/>
+      <x:c r="M21" s="28" t="s"/>
+    </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="23" t="s">
+      <x:c r="B24" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C24" s="24" t="s"/>
-      <x:c r="D24" s="24" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="25" t="s"/>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="31" t="s"/>
+      <x:c r="F24" s="31" t="s"/>
     </x:row>
     <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+      <x:c r="B25" s="32" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="s">
+      <x:c r="C25" s="33" t="s"/>
+      <x:c r="D25" s="33" t="s"/>
+      <x:c r="E25" s="33" t="s"/>
+      <x:c r="F25" s="34" t="s">
         <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="29" t="s">
+      <x:c r="B26" s="35" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="30" t="s"/>
-      <x:c r="D26" s="30" t="s"/>
-      <x:c r="E26" s="30" t="s"/>
-      <x:c r="F26" s="31" t="n">
+      <x:c r="C26" s="36" t="s"/>
+      <x:c r="D26" s="36" t="s"/>
+      <x:c r="E26" s="36" t="s"/>
+      <x:c r="F26" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="29" t="s">
+      <x:c r="B27" s="35" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
+      <x:c r="C27" s="36" t="s"/>
+      <x:c r="D27" s="36" t="s"/>
+      <x:c r="E27" s="36" t="s"/>
+      <x:c r="F27" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="29" t="s">
+      <x:c r="B28" s="35" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C28" s="30" t="s"/>
-      <x:c r="D28" s="30" t="s"/>
-      <x:c r="E28" s="30" t="s"/>
-      <x:c r="F28" s="31" t="n">
+      <x:c r="C28" s="36" t="s"/>
+      <x:c r="D28" s="36" t="s"/>
+      <x:c r="E28" s="36" t="s"/>
+      <x:c r="F28" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="29" t="s">
+      <x:c r="B29" s="35" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C29" s="30" t="s"/>
-      <x:c r="D29" s="30" t="s"/>
-      <x:c r="E29" s="30" t="s"/>
-      <x:c r="F29" s="31" t="n">
+      <x:c r="C29" s="36" t="s"/>
+      <x:c r="D29" s="36" t="s"/>
+      <x:c r="E29" s="36" t="s"/>
+      <x:c r="F29" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="29" t="s">
+      <x:c r="B30" s="35" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C30" s="30" t="s"/>
-      <x:c r="D30" s="30" t="s"/>
-      <x:c r="E30" s="30" t="s"/>
-      <x:c r="F30" s="31" t="n">
+      <x:c r="C30" s="36" t="s"/>
+      <x:c r="D30" s="36" t="s"/>
+      <x:c r="E30" s="36" t="s"/>
+      <x:c r="F30" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="29" t="s">
+      <x:c r="B31" s="35" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C31" s="30" t="s"/>
-      <x:c r="D31" s="30" t="s"/>
-      <x:c r="E31" s="30" t="s"/>
-      <x:c r="F31" s="31" t="n">
+      <x:c r="C31" s="36" t="s"/>
+      <x:c r="D31" s="36" t="s"/>
+      <x:c r="E31" s="36" t="s"/>
+      <x:c r="F31" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="29" t="s">
+      <x:c r="B32" s="35" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C32" s="30" t="s"/>
-      <x:c r="D32" s="30" t="s"/>
-      <x:c r="E32" s="30" t="s"/>
-      <x:c r="F32" s="31" t="n">
+      <x:c r="C32" s="36" t="s"/>
+      <x:c r="D32" s="36" t="s"/>
+      <x:c r="E32" s="36" t="s"/>
+      <x:c r="F32" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="29" t="s">
+      <x:c r="B33" s="35" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C33" s="30" t="s"/>
-      <x:c r="D33" s="30" t="s"/>
-      <x:c r="E33" s="30" t="s"/>
-      <x:c r="F33" s="31" t="n">
+      <x:c r="C33" s="36" t="s"/>
+      <x:c r="D33" s="36" t="s"/>
+      <x:c r="E33" s="36" t="s"/>
+      <x:c r="F33" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="29" t="s">
+      <x:c r="B34" s="35" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C34" s="30" t="s"/>
-      <x:c r="D34" s="30" t="s"/>
-      <x:c r="E34" s="30" t="s"/>
-      <x:c r="F34" s="31" t="n">
+      <x:c r="C34" s="36" t="s"/>
+      <x:c r="D34" s="36" t="s"/>
+      <x:c r="E34" s="36" t="s"/>
+      <x:c r="F34" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="32" t="s">
+      <x:c r="B35" s="38" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C35" s="33" t="s"/>
-      <x:c r="D35" s="33" t="s"/>
-      <x:c r="E35" s="33" t="s"/>
-      <x:c r="F35" s="34" t="n">
+      <x:c r="C35" s="39" t="s"/>
+      <x:c r="D35" s="39" t="s"/>
+      <x:c r="E35" s="39" t="s"/>
+      <x:c r="F35" s="40" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -1062,7 +1062,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -1130,7 +1130,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>1</x:v>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,9 +22,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -217,7 +253,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -262,21 +298,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -286,6 +307,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -536,7 +564,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -547,74 +575,68 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -645,56 +667,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -709,63 +683,75 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1064,18 +1050,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1093,681 +1067,693 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s"/>
-      <x:c r="E8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s"/>
+      <x:c r="E9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>45825.0450347222</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>45825.0450578704</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1546810</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="18">
         <x:v>45825.0561574074</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s"/>
-      <x:c r="E9" s="19" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H9" s="20">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>45827.2931018519</x:v>
       </x:c>
-      <x:c r="I9" s="20">
+      <x:c r="I11" s="16">
         <x:v>45827.293125</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1435677</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="18">
         <x:v>45827.2985763889</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="22" t="s">
+      <x:c r="M11" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45825.2509606481</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45825.2509837963</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>2744256</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45825.8750462963</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I13" s="19">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s"/>
+      <x:c r="E16" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s"/>
+      <x:c r="E17" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C10" s="22" t="s">
+      <x:c r="D18" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D10" s="23" t="s"/>
-      <x:c r="E10" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F10" s="22" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G10" s="22" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H10" s="24">
-        <x:v>45825.2509606481</x:v>
-      </x:c>
-      <x:c r="I10" s="24">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J10" s="23" t="n">
-        <x:v>2744256</x:v>
-      </x:c>
-      <x:c r="K10" s="25" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L10" s="26">
-        <x:v>45825.8750462963</x:v>
-      </x:c>
-      <x:c r="M10" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="22" t="s">
+      <x:c r="F18" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I20" s="19">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C11" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D11" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E11" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F11" s="22" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G11" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H11" s="24">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I11" s="27">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J11" s="23" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K11" s="25" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L11" s="26">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M11" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D12" s="23" t="s"/>
-      <x:c r="E12" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F12" s="22" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G12" s="22" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H12" s="24">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I12" s="24">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J12" s="23" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K12" s="25" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L12" s="26">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M12" s="22" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D13" s="23" t="s"/>
-      <x:c r="E13" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F13" s="22" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G13" s="22" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H13" s="24">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I13" s="24">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J13" s="23" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K13" s="25" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L13" s="26">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M13" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="22" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F14" s="22" t="s">
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G14" s="22" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H14" s="24">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I14" s="24">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J14" s="23" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K14" s="25" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L14" s="26">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M14" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="22" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F15" s="22" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G15" s="22" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H15" s="24">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I15" s="24">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J15" s="23" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K15" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="26">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M15" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="22" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D16" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E16" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F16" s="22" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G16" s="22" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H16" s="24">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I16" s="24">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J16" s="23" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K16" s="25" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L16" s="26">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M16" s="22" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="22" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C17" s="22" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D17" s="23" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E17" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F17" s="22" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G17" s="22" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H17" s="24">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I17" s="24">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J17" s="23" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K17" s="25" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L17" s="26">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M17" s="22" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="22" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C18" s="22" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D18" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E18" s="22" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F18" s="22" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G18" s="22" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H18" s="24">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I18" s="27">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J18" s="23" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K18" s="25" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L18" s="26">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M18" s="22" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C19" s="22" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D19" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E19" s="22" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F19" s="22" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G19" s="22" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H19" s="24">
+      <x:c r="E21" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I19" s="27">
+      <x:c r="I21" s="19">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J19" s="23" t="n">
+      <x:c r="J21" s="15" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K19" s="25" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L19" s="26">
+      <x:c r="L21" s="18">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M19" s="22" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B20" s="28" t="s"/>
-      <x:c r="C20" s="28" t="s"/>
-      <x:c r="D20" s="28" t="s"/>
-      <x:c r="E20" s="28" t="s"/>
-      <x:c r="F20" s="28" t="s"/>
-      <x:c r="G20" s="28" t="s"/>
-      <x:c r="H20" s="28" t="s"/>
-      <x:c r="I20" s="28" t="s"/>
-      <x:c r="J20" s="28" t="s"/>
-      <x:c r="K20" s="28" t="s"/>
-      <x:c r="L20" s="28" t="s"/>
-      <x:c r="M20" s="28" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B21" s="28" t="s"/>
-      <x:c r="C21" s="28" t="s"/>
-      <x:c r="D21" s="28" t="s"/>
-      <x:c r="E21" s="28" t="s"/>
-      <x:c r="F21" s="28" t="s"/>
-      <x:c r="G21" s="28" t="s"/>
-      <x:c r="H21" s="28" t="s"/>
-      <x:c r="I21" s="28" t="s"/>
-      <x:c r="J21" s="28" t="s"/>
-      <x:c r="K21" s="28" t="s"/>
-      <x:c r="L21" s="28" t="s"/>
-      <x:c r="M21" s="28" t="s"/>
+      <x:c r="M21" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="31" t="s"/>
-      <x:c r="F24" s="31" t="s"/>
+      <x:c r="B24" s="20" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C24" s="21" t="s"/>
+      <x:c r="D24" s="21" t="s"/>
+      <x:c r="E24" s="22" t="s"/>
+      <x:c r="F24" s="22" t="s"/>
     </x:row>
     <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="32" t="s">
+      <x:c r="B25" s="23" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C25" s="24" t="s"/>
+      <x:c r="D25" s="24" t="s"/>
+      <x:c r="E25" s="24" t="s"/>
+      <x:c r="F25" s="25" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C25" s="33" t="s"/>
-      <x:c r="D25" s="33" t="s"/>
-      <x:c r="E25" s="33" t="s"/>
-      <x:c r="F25" s="34" t="s">
-        <x:v>60</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="35" t="s">
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="36" t="s"/>
-      <x:c r="D26" s="36" t="s"/>
-      <x:c r="E26" s="36" t="s"/>
-      <x:c r="F26" s="37" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="35" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C27" s="36" t="s"/>
-      <x:c r="D27" s="36" t="s"/>
-      <x:c r="E27" s="36" t="s"/>
-      <x:c r="F27" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="35" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C28" s="36" t="s"/>
-      <x:c r="D28" s="36" t="s"/>
-      <x:c r="E28" s="36" t="s"/>
-      <x:c r="F28" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="35" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C29" s="36" t="s"/>
-      <x:c r="D29" s="36" t="s"/>
-      <x:c r="E29" s="36" t="s"/>
-      <x:c r="F29" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="35" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C30" s="36" t="s"/>
-      <x:c r="D30" s="36" t="s"/>
-      <x:c r="E30" s="36" t="s"/>
-      <x:c r="F30" s="37" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="35" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C31" s="36" t="s"/>
-      <x:c r="D31" s="36" t="s"/>
-      <x:c r="E31" s="36" t="s"/>
-      <x:c r="F31" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="35" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C32" s="36" t="s"/>
-      <x:c r="D32" s="36" t="s"/>
-      <x:c r="E32" s="36" t="s"/>
-      <x:c r="F32" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="35" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C33" s="36" t="s"/>
-      <x:c r="D33" s="36" t="s"/>
-      <x:c r="E33" s="36" t="s"/>
-      <x:c r="F33" s="37" t="n">
-        <x:v>1</x:v>
-      </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="35" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C34" s="36" t="s"/>
-      <x:c r="D34" s="36" t="s"/>
-      <x:c r="E34" s="36" t="s"/>
-      <x:c r="F34" s="37" t="n">
+      <x:c r="B34" s="26" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="38" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C35" s="39" t="s"/>
-      <x:c r="D35" s="39" t="s"/>
-      <x:c r="E35" s="39" t="s"/>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="B35" s="29" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s"/>
+      <x:c r="D35" s="30" t="s"/>
+      <x:c r="E35" s="30" t="s"/>
+      <x:c r="F35" s="31" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -564,11 +564,14 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -636,7 +639,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -666,6 +669,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1000,7 +1007,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>45809</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -1072,688 +1081,688 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="12" t="s"/>
+      <x:c r="E8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>45832.3271759259</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>45832.3271990741</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>16854</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>45832.3384259259</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s"/>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="D9" s="12" t="s"/>
+      <x:c r="E9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="F9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>45826.3053472222</x:v>
       </x:c>
-      <x:c r="I9" s="12">
+      <x:c r="I9" s="13">
         <x:v>45826.3053703704</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>1434444</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>45826.3117939815</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="B10" s="15" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="C10" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="F10" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="G10" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="H10" s="17">
         <x:v>45825.0450347222</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="17">
         <x:v>45825.0450578704</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="16" t="n">
         <x:v>1546810</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="18">
+      <x:c r="L10" s="19">
         <x:v>45825.0561574074</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
+      <x:c r="M10" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
+      <x:c r="B11" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="C11" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="D11" s="16" t="s"/>
+      <x:c r="E11" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="F11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="G11" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="H11" s="17">
         <x:v>45827.2931018519</x:v>
       </x:c>
-      <x:c r="I11" s="16">
+      <x:c r="I11" s="17">
         <x:v>45827.293125</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="16" t="n">
         <x:v>1435677</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="18">
+      <x:c r="L11" s="19">
         <x:v>45827.2985763889</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="M11" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
+      <x:c r="B12" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C12" s="14" t="s">
+      <x:c r="C12" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="F12" s="15" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="H12" s="17">
         <x:v>45825.2509606481</x:v>
       </x:c>
-      <x:c r="I12" s="16">
+      <x:c r="I12" s="17">
         <x:v>45825.2509837963</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="16" t="n">
         <x:v>2744256</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L12" s="18">
+      <x:c r="L12" s="19">
         <x:v>45825.8750462963</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
+      <x:c r="M12" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
+      <x:c r="B13" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="C13" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
+      <x:c r="D13" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="E13" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="F13" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="H13" s="17">
         <x:v>45826.1308796296</x:v>
       </x:c>
-      <x:c r="I13" s="19">
+      <x:c r="I13" s="20">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="16" t="n">
         <x:v>2734401</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="L13" s="18">
+      <x:c r="L13" s="19">
         <x:v>45826.1478935185</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
+      <x:c r="M13" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
+      <x:c r="B14" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C14" s="14" t="s">
+      <x:c r="C14" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s"/>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="D14" s="16" t="s"/>
+      <x:c r="E14" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="F14" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="G14" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="H14" s="17">
         <x:v>45827.2810416667</x:v>
       </x:c>
-      <x:c r="I14" s="16">
+      <x:c r="I14" s="17">
         <x:v>45827.2810648148</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="16" t="n">
         <x:v>1616</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L14" s="18">
+      <x:c r="L14" s="19">
         <x:v>45827.2917592593</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
+      <x:c r="M14" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
+      <x:c r="B15" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C15" s="14" t="s">
+      <x:c r="C15" s="15" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s"/>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="D15" s="16" t="s"/>
+      <x:c r="E15" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="F15" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="G15" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="H15" s="17">
         <x:v>45825.2634953704</x:v>
       </x:c>
-      <x:c r="I15" s="16">
+      <x:c r="I15" s="17">
         <x:v>45825.2635300926</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="16" t="n">
         <x:v>274001</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L15" s="18">
+      <x:c r="L15" s="19">
         <x:v>45825.2871759259</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
+      <x:c r="M15" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
+      <x:c r="B16" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="C16" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s"/>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="D16" s="16" t="s"/>
+      <x:c r="E16" s="15" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="F16" s="15" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="G16" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="H16" s="17">
         <x:v>45826.3109259259</x:v>
       </x:c>
-      <x:c r="I16" s="16">
+      <x:c r="I16" s="17">
         <x:v>45826.3109375</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J16" s="16" t="n">
         <x:v>1432235</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L16" s="18">
+      <x:c r="L16" s="19">
         <x:v>45826.3168865741</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
+      <x:c r="M16" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
+      <x:c r="B17" s="15" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="C17" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s"/>
-      <x:c r="E17" s="14" t="s">
+      <x:c r="D17" s="16" t="s"/>
+      <x:c r="E17" s="15" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="F17" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="G17" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H17" s="16">
+      <x:c r="H17" s="17">
         <x:v>45825.5009259259</x:v>
       </x:c>
-      <x:c r="I17" s="16">
+      <x:c r="I17" s="17">
         <x:v>45825.5010185185</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
+      <x:c r="J17" s="16" t="n">
         <x:v>1434267</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="K17" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="18">
+      <x:c r="L17" s="19">
         <x:v>45827.2850694444</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="s">
+      <x:c r="M17" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
+      <x:c r="B18" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="C18" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s">
+      <x:c r="D18" s="16" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="E18" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="F18" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="G18" s="15" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H18" s="16">
+      <x:c r="H18" s="17">
         <x:v>45825.1485185185</x:v>
       </x:c>
-      <x:c r="I18" s="16">
+      <x:c r="I18" s="17">
         <x:v>45825.1485416667</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="n">
+      <x:c r="J18" s="16" t="n">
         <x:v>15135861</x:v>
       </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="K18" s="18" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="L18" s="18">
+      <x:c r="L18" s="19">
         <x:v>45825.1676388889</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
+      <x:c r="M18" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
+      <x:c r="B19" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C19" s="14" t="s">
+      <x:c r="C19" s="15" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
+      <x:c r="D19" s="16" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E19" s="14" t="s">
+      <x:c r="E19" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="F19" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="G19" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H19" s="16">
+      <x:c r="H19" s="17">
         <x:v>45827.0419791667</x:v>
       </x:c>
-      <x:c r="I19" s="16">
+      <x:c r="I19" s="17">
         <x:v>45827.0420138889</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
+      <x:c r="J19" s="16" t="n">
         <x:v>52268</x:v>
       </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="K19" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L19" s="18">
+      <x:c r="L19" s="19">
         <x:v>45827.0460069444</x:v>
       </x:c>
-      <x:c r="M19" s="14" t="s">
+      <x:c r="M19" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
+      <x:c r="B20" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C20" s="14" t="s">
+      <x:c r="C20" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="s">
+      <x:c r="D20" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E20" s="14" t="s">
+      <x:c r="E20" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="F20" s="15" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
+      <x:c r="G20" s="15" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H20" s="16">
+      <x:c r="H20" s="17">
         <x:v>45826.1449768519</x:v>
       </x:c>
-      <x:c r="I20" s="19">
+      <x:c r="I20" s="20">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="n">
+      <x:c r="J20" s="16" t="n">
         <x:v>1435666</x:v>
       </x:c>
-      <x:c r="K20" s="17" t="n">
+      <x:c r="K20" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="18">
+      <x:c r="L20" s="19">
         <x:v>45826.2821412037</x:v>
       </x:c>
-      <x:c r="M20" s="14" t="s">
+      <x:c r="M20" s="15" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
+      <x:c r="B21" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C21" s="14" t="s">
+      <x:c r="C21" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="s">
+      <x:c r="D21" s="16" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E21" s="14" t="s">
+      <x:c r="E21" s="15" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="F21" s="15" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="G21" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H21" s="16">
+      <x:c r="H21" s="17">
         <x:v>45827.1931712963</x:v>
       </x:c>
-      <x:c r="I21" s="19">
+      <x:c r="I21" s="20">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
+      <x:c r="J21" s="16" t="n">
         <x:v>1234312</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="K21" s="18" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L21" s="18">
+      <x:c r="L21" s="19">
         <x:v>45827.2195833333</x:v>
       </x:c>
-      <x:c r="M21" s="14" t="s">
+      <x:c r="M21" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="20" t="s">
+      <x:c r="B24" s="21" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C24" s="21" t="s"/>
-      <x:c r="D24" s="21" t="s"/>
-      <x:c r="E24" s="22" t="s"/>
-      <x:c r="F24" s="22" t="s"/>
+      <x:c r="C24" s="22" t="s"/>
+      <x:c r="D24" s="22" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="23" t="s"/>
     </x:row>
     <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="23" t="s">
+      <x:c r="B25" s="24" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C25" s="24" t="s"/>
-      <x:c r="D25" s="24" t="s"/>
-      <x:c r="E25" s="24" t="s"/>
-      <x:c r="F25" s="25" t="s">
+      <x:c r="C25" s="25" t="s"/>
+      <x:c r="D25" s="25" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="26" t="s">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+      <x:c r="B26" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="C26" s="28" t="s"/>
+      <x:c r="D26" s="28" t="s"/>
+      <x:c r="E26" s="28" t="s"/>
+      <x:c r="F26" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
+      <x:c r="B27" s="27" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="C27" s="28" t="s"/>
+      <x:c r="D27" s="28" t="s"/>
+      <x:c r="E27" s="28" t="s"/>
+      <x:c r="F27" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
+      <x:c r="B28" s="27" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+      <x:c r="B29" s="27" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+      <x:c r="B30" s="27" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="C30" s="28" t="s"/>
+      <x:c r="D30" s="28" t="s"/>
+      <x:c r="E30" s="28" t="s"/>
+      <x:c r="F30" s="29" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
+      <x:c r="B31" s="27" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="C31" s="28" t="s"/>
+      <x:c r="D31" s="28" t="s"/>
+      <x:c r="E31" s="28" t="s"/>
+      <x:c r="F31" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
+      <x:c r="B32" s="27" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C32" s="28" t="s"/>
+      <x:c r="D32" s="28" t="s"/>
+      <x:c r="E32" s="28" t="s"/>
+      <x:c r="F32" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
+      <x:c r="B33" s="27" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="C33" s="28" t="s"/>
+      <x:c r="D33" s="28" t="s"/>
+      <x:c r="E33" s="28" t="s"/>
+      <x:c r="F33" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
+      <x:c r="B34" s="27" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="C34" s="28" t="s"/>
+      <x:c r="D34" s="28" t="s"/>
+      <x:c r="E34" s="28" t="s"/>
+      <x:c r="F34" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="29" t="s">
+      <x:c r="B35" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C35" s="30" t="s"/>
-      <x:c r="D35" s="30" t="s"/>
-      <x:c r="E35" s="30" t="s"/>
-      <x:c r="F35" s="31" t="n">
+      <x:c r="C35" s="31" t="s"/>
+      <x:c r="D35" s="31" t="s"/>
+      <x:c r="E35" s="31" t="s"/>
+      <x:c r="F35" s="32" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,9 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -253,7 +256,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -293,6 +296,22 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -564,12 +583,15 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -587,59 +609,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -670,95 +692,99 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -987,40 +1013,40 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>45809</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
@@ -1081,688 +1107,688 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="C7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="s"/>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="D8" s="13" t="s"/>
+      <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="G8" s="13" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
         <x:v>45832.3271759259</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>45832.3271990741</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="13" t="n">
         <x:v>16854</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="14">
         <x:v>45832.3384259259</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>18</x:v>
+      <x:c r="M8" s="13" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
+      <x:c r="B9" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="14">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J9" s="13" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K9" s="15" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="14">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="s"/>
+      <x:c r="E10" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H10" s="18">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M10" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D9" s="12" t="s"/>
-      <x:c r="E9" s="12" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="18">
+        <x:v>45827.2931018519</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>45827.293125</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="n">
+        <x:v>1435677</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L11" s="20">
+        <x:v>45827.2985763889</x:v>
+      </x:c>
+      <x:c r="M11" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H12" s="18">
+        <x:v>45825.2509606481</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>45825.2509837963</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="n">
+        <x:v>2744256</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>45825.8750462963</x:v>
+      </x:c>
+      <x:c r="M12" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H13" s="18">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I13" s="21">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L13" s="20">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M13" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="s"/>
+      <x:c r="E14" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H14" s="18">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L14" s="20">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M14" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s"/>
+      <x:c r="E15" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H15" s="18">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M15" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="s"/>
+      <x:c r="E16" s="16" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H16" s="18">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I16" s="18">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M16" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="s"/>
+      <x:c r="E17" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H17" s="18">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M17" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="16" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="s">
+      <x:c r="D18" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I9" s="13">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K9" s="14" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="F18" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H18" s="18">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M18" s="16" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H19" s="18">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M19" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H20" s="18">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I20" s="21">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M20" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D11" s="16" t="s"/>
-      <x:c r="E11" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H11" s="17">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J11" s="16" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45827.2985763889</x:v>
-      </x:c>
-      <x:c r="M11" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>45825.2509606481</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="n">
-        <x:v>2744256</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45825.8750462963</x:v>
-      </x:c>
-      <x:c r="M12" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D13" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="s">
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I13" s="20">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M13" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M14" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C15" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H15" s="17">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C16" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D16" s="16" t="s"/>
-      <x:c r="E16" s="15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F16" s="15" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H16" s="17">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I16" s="17">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J16" s="16" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M16" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C17" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D17" s="16" t="s"/>
-      <x:c r="E17" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H17" s="17">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I17" s="17">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J17" s="16" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="15" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="E21" s="16" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H21" s="18">
+        <x:v>45827.1931712963</x:v>
+      </x:c>
+      <x:c r="I21" s="21">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="n">
+        <x:v>1234312</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>18810</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>45827.2195833333</x:v>
+      </x:c>
+      <x:c r="M21" s="16" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="D18" s="16" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E18" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G18" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H18" s="17">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J18" s="16" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M18" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C19" s="15" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D19" s="16" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E19" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H19" s="17">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J19" s="16" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M19" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C20" s="15" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D20" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E20" s="15" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G20" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H20" s="17">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I20" s="20">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J20" s="16" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M20" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="15" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C21" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D21" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E21" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F21" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G21" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H21" s="17">
-        <x:v>45827.1931712963</x:v>
-      </x:c>
-      <x:c r="I21" s="20">
-        <x:v>44197</x:v>
-      </x:c>
-      <x:c r="J21" s="16" t="n">
-        <x:v>1234312</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>18810</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>45827.2195833333</x:v>
-      </x:c>
-      <x:c r="M21" s="15" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="21" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C24" s="22" t="s"/>
-      <x:c r="D24" s="22" t="s"/>
-      <x:c r="E24" s="23" t="s"/>
-      <x:c r="F24" s="23" t="s"/>
+      <x:c r="B24" s="22" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="s"/>
+      <x:c r="D24" s="23" t="s"/>
+      <x:c r="E24" s="24" t="s"/>
+      <x:c r="F24" s="24" t="s"/>
     </x:row>
     <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="24" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C25" s="25" t="s"/>
-      <x:c r="D25" s="25" t="s"/>
-      <x:c r="E25" s="25" t="s"/>
-      <x:c r="F25" s="26" t="s">
+      <x:c r="B25" s="25" t="s">
         <x:v>72</x:v>
       </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="s">
+        <x:v>73</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C26" s="28" t="s"/>
-      <x:c r="D26" s="28" t="s"/>
-      <x:c r="E26" s="28" t="s"/>
-      <x:c r="F26" s="29" t="n">
+      <x:c r="B26" s="28" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="27" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="B27" s="28" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="27" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="n">
+      <x:c r="B28" s="28" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C28" s="29" t="s"/>
+      <x:c r="D28" s="29" t="s"/>
+      <x:c r="E28" s="29" t="s"/>
+      <x:c r="F28" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="27" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
+      <x:c r="B29" s="28" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C29" s="29" t="s"/>
+      <x:c r="D29" s="29" t="s"/>
+      <x:c r="E29" s="29" t="s"/>
+      <x:c r="F29" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="27" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C30" s="28" t="s"/>
-      <x:c r="D30" s="28" t="s"/>
-      <x:c r="E30" s="28" t="s"/>
-      <x:c r="F30" s="29" t="n">
+      <x:c r="B30" s="28" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C30" s="29" t="s"/>
+      <x:c r="D30" s="29" t="s"/>
+      <x:c r="E30" s="29" t="s"/>
+      <x:c r="F30" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="27" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C31" s="28" t="s"/>
-      <x:c r="D31" s="28" t="s"/>
-      <x:c r="E31" s="28" t="s"/>
-      <x:c r="F31" s="29" t="n">
+      <x:c r="B31" s="28" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C31" s="29" t="s"/>
+      <x:c r="D31" s="29" t="s"/>
+      <x:c r="E31" s="29" t="s"/>
+      <x:c r="F31" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="27" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C32" s="28" t="s"/>
-      <x:c r="D32" s="28" t="s"/>
-      <x:c r="E32" s="28" t="s"/>
-      <x:c r="F32" s="29" t="n">
+      <x:c r="B32" s="28" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="27" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C33" s="28" t="s"/>
-      <x:c r="D33" s="28" t="s"/>
-      <x:c r="E33" s="28" t="s"/>
-      <x:c r="F33" s="29" t="n">
+      <x:c r="B33" s="28" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C33" s="29" t="s"/>
+      <x:c r="D33" s="29" t="s"/>
+      <x:c r="E33" s="29" t="s"/>
+      <x:c r="F33" s="30" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="27" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C34" s="28" t="s"/>
-      <x:c r="D34" s="28" t="s"/>
-      <x:c r="E34" s="28" t="s"/>
-      <x:c r="F34" s="29" t="n">
+      <x:c r="B34" s="28" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="30" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C35" s="31" t="s"/>
-      <x:c r="D35" s="31" t="s"/>
-      <x:c r="E35" s="31" t="s"/>
-      <x:c r="F35" s="32" t="n">
+      <x:c r="B35" s="31" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C35" s="32" t="s"/>
+      <x:c r="D35" s="32" t="s"/>
+      <x:c r="E35" s="32" t="s"/>
+      <x:c r="F35" s="33" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -64,6 +64,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -253,10 +289,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -301,27 +339,12 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
@@ -588,15 +611,15 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -609,59 +632,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -692,99 +715,87 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1013,74 +1024,72 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
-      <x:c r="N1" s="1" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
-      <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
-      <x:c r="N2" s="1" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:28">
-      <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
-      <x:c r="N3" s="3" t="s"/>
-    </x:row>
-    <x:row r="4" spans="1:28">
-      <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -1105,7 +1114,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1145,655 +1154,705 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s"/>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="G8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="13" t="s"/>
+      <x:c r="C9" s="13" t="s"/>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s"/>
+      <x:c r="F9" s="13" t="s"/>
+      <x:c r="G9" s="13" t="s"/>
+      <x:c r="H9" s="13" t="s"/>
+      <x:c r="I9" s="13" t="s"/>
+      <x:c r="J9" s="13" t="s"/>
+      <x:c r="K9" s="13" t="s"/>
+      <x:c r="L9" s="13" t="s"/>
+      <x:c r="M9" s="13" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>45832.3271759259</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I10" s="16">
         <x:v>45832.3271990741</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>16854</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L10" s="18">
         <x:v>45832.3384259259</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="13" t="s">
+      <x:c r="M10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="18">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="18">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45827.2931018519</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>45827.293125</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1435677</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L13" s="18">
+        <x:v>45827.2985763889</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45825.2509606481</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45825.2509837963</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>2744256</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L14" s="18">
+        <x:v>45825.8750462963</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L15" s="18">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s"/>
+      <x:c r="E16" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s"/>
+      <x:c r="E17" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s"/>
+      <x:c r="E18" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s"/>
+      <x:c r="E19" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>45827.1931712963</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1234312</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>18810</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>45827.2195833333</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="19" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="s"/>
+      <x:c r="D26" s="20" t="s"/>
+      <x:c r="E26" s="21" t="s"/>
+      <x:c r="F26" s="21" t="s"/>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B27" s="22" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="s"/>
+      <x:c r="D27" s="23" t="s"/>
+      <x:c r="E27" s="23" t="s"/>
+      <x:c r="F27" s="24" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="25" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="25" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="25" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="25" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="25" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="25" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C35" s="26" t="s"/>
+      <x:c r="D35" s="26" t="s"/>
+      <x:c r="E35" s="26" t="s"/>
+      <x:c r="F35" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="25" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="28" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C37" s="29" t="s"/>
+      <x:c r="D37" s="29" t="s"/>
+      <x:c r="E37" s="29" t="s"/>
+      <x:c r="F37" s="30" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F9" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="14">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J9" s="13" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="14">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M9" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="s"/>
-      <x:c r="E10" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H10" s="18">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J10" s="17" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="20">
-        <x:v>45827.2985763889</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
-        <x:v>45825.2509606481</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="n">
-        <x:v>2744256</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L12" s="20">
-        <x:v>45825.8750462963</x:v>
-      </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I13" s="21">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L13" s="20">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s"/>
-      <x:c r="E14" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J14" s="17" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L14" s="20">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s"/>
-      <x:c r="E15" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L15" s="20">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s"/>
-      <x:c r="E16" s="16" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J16" s="17" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="s"/>
-      <x:c r="E17" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H17" s="18">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I17" s="18">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="20">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I18" s="18">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J18" s="17" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L18" s="20">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E19" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H19" s="18">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I19" s="18">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L19" s="20">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="16" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E20" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H20" s="18">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I20" s="21">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J20" s="17" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="20">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D21" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E21" s="16" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>45827.1931712963</x:v>
-      </x:c>
-      <x:c r="I21" s="21">
-        <x:v>44197</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1234312</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
-        <x:v>18810</x:v>
-      </x:c>
-      <x:c r="L21" s="20">
-        <x:v>45827.2195833333</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C24" s="23" t="s"/>
-      <x:c r="D24" s="23" t="s"/>
-      <x:c r="E24" s="24" t="s"/>
-      <x:c r="F24" s="24" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="25" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="28" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="28" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="28" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C28" s="29" t="s"/>
-      <x:c r="D28" s="29" t="s"/>
-      <x:c r="E28" s="29" t="s"/>
-      <x:c r="F28" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="28" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C29" s="29" t="s"/>
-      <x:c r="D29" s="29" t="s"/>
-      <x:c r="E29" s="29" t="s"/>
-      <x:c r="F29" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="28" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C30" s="29" t="s"/>
-      <x:c r="D30" s="29" t="s"/>
-      <x:c r="E30" s="29" t="s"/>
-      <x:c r="F30" s="30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="28" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C31" s="29" t="s"/>
-      <x:c r="D31" s="29" t="s"/>
-      <x:c r="E31" s="29" t="s"/>
-      <x:c r="F31" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="28" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="28" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C33" s="29" t="s"/>
-      <x:c r="D33" s="29" t="s"/>
-      <x:c r="E33" s="29" t="s"/>
-      <x:c r="F33" s="30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="28" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C34" s="29" t="s"/>
-      <x:c r="D34" s="29" t="s"/>
-      <x:c r="E34" s="29" t="s"/>
-      <x:c r="F34" s="30" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="31" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C35" s="32" t="s"/>
-      <x:c r="D35" s="32" t="s"/>
-      <x:c r="E35" s="32" t="s"/>
-      <x:c r="F35" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    </x:row>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2752,12 +2811,10 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="15">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B24:F24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B26:F26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
@@ -2767,6 +2824,8 @@
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -64,42 +64,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Amateur</x:t>
@@ -294,7 +258,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -338,13 +302,20 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
@@ -606,7 +577,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -614,12 +585,12 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -632,13 +603,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -650,41 +615,50 @@
     <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -715,24 +689,16 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -747,55 +713,71 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1114,7 +1096,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1154,705 +1136,655 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="13" t="s"/>
+      <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="G8" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="H8" s="14">
+        <x:v>45832.3271759259</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>45832.3271990741</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="n">
+        <x:v>16854</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>45832.3384259259</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="F9" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="G9" s="13" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
+      <x:c r="H9" s="14">
+        <x:v>45826.3053472222</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>45826.3053703704</x:v>
+      </x:c>
+      <x:c r="J9" s="13" t="n">
+        <x:v>1434444</x:v>
+      </x:c>
+      <x:c r="K9" s="15" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="14">
+        <x:v>45826.3117939815</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="M8" s="9" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="16" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="s"/>
+      <x:c r="E10" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="13" t="s"/>
-      <x:c r="C9" s="13" t="s"/>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s"/>
-      <x:c r="F9" s="13" t="s"/>
-      <x:c r="G9" s="13" t="s"/>
-      <x:c r="H9" s="13" t="s"/>
-      <x:c r="I9" s="13" t="s"/>
-      <x:c r="J9" s="13" t="s"/>
-      <x:c r="K9" s="13" t="s"/>
-      <x:c r="L9" s="13" t="s"/>
-      <x:c r="M9" s="13" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
+      <x:c r="G10" s="16" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="14" t="s">
+      <x:c r="H10" s="18">
+        <x:v>45825.0450347222</x:v>
+      </x:c>
+      <x:c r="I10" s="18">
+        <x:v>45825.0450578704</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="n">
+        <x:v>1546810</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="20">
+        <x:v>45825.0561574074</x:v>
+      </x:c>
+      <x:c r="M10" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="16" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="s"/>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="C11" s="16" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="D11" s="17" t="s"/>
+      <x:c r="E11" s="16" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="F11" s="16" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="G11" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H11" s="18">
+        <x:v>45827.2931018519</x:v>
+      </x:c>
+      <x:c r="I11" s="18">
+        <x:v>45827.293125</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="n">
+        <x:v>1435677</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L11" s="20">
+        <x:v>45827.2985763889</x:v>
+      </x:c>
+      <x:c r="M11" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="16" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H12" s="18">
+        <x:v>45825.2509606481</x:v>
+      </x:c>
+      <x:c r="I12" s="18">
+        <x:v>45825.2509837963</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="n">
+        <x:v>2744256</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L12" s="20">
+        <x:v>45825.8750462963</x:v>
+      </x:c>
+      <x:c r="M12" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H13" s="18">
+        <x:v>45826.1308796296</x:v>
+      </x:c>
+      <x:c r="I13" s="18">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
+        <x:v>2734401</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L13" s="20">
+        <x:v>45826.1478935185</x:v>
+      </x:c>
+      <x:c r="M13" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="s"/>
+      <x:c r="E14" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H14" s="18">
+        <x:v>45827.2810416667</x:v>
+      </x:c>
+      <x:c r="I14" s="18">
+        <x:v>45827.2810648148</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="n">
+        <x:v>1616</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="18">
-        <x:v>45832.3384259259</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="L14" s="20">
+        <x:v>45827.2917592593</x:v>
+      </x:c>
+      <x:c r="M14" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="s"/>
+      <x:c r="E15" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H15" s="18">
+        <x:v>45825.2634953704</x:v>
+      </x:c>
+      <x:c r="I15" s="18">
+        <x:v>45825.2635300926</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="n">
+        <x:v>274001</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L15" s="20">
+        <x:v>45825.2871759259</x:v>
+      </x:c>
+      <x:c r="M15" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="s"/>
+      <x:c r="E16" s="16" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H16" s="18">
+        <x:v>45826.3109259259</x:v>
+      </x:c>
+      <x:c r="I16" s="18">
+        <x:v>45826.3109375</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="n">
+        <x:v>1432235</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L16" s="20">
+        <x:v>45826.3168865741</x:v>
+      </x:c>
+      <x:c r="M16" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="16" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="s"/>
+      <x:c r="E17" s="16" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H17" s="18">
+        <x:v>45825.5009259259</x:v>
+      </x:c>
+      <x:c r="I17" s="18">
+        <x:v>45825.5010185185</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="n">
+        <x:v>1434267</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="20">
+        <x:v>45827.2850694444</x:v>
+      </x:c>
+      <x:c r="M17" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="16" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
+      <x:c r="E18" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H18" s="18">
+        <x:v>45825.1485185185</x:v>
+      </x:c>
+      <x:c r="I18" s="18">
+        <x:v>45825.1485416667</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="n">
+        <x:v>15135861</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L18" s="20">
+        <x:v>45825.1676388889</x:v>
+      </x:c>
+      <x:c r="M18" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="16" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H19" s="18">
+        <x:v>45827.0419791667</x:v>
+      </x:c>
+      <x:c r="I19" s="18">
+        <x:v>45827.0420138889</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="n">
+        <x:v>52268</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="20">
+        <x:v>45827.0460069444</x:v>
+      </x:c>
+      <x:c r="M19" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H20" s="18">
+        <x:v>45826.1449768519</x:v>
+      </x:c>
+      <x:c r="I20" s="18">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="n">
+        <x:v>1435666</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="20">
+        <x:v>45826.2821412037</x:v>
+      </x:c>
+      <x:c r="M20" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="16" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H21" s="18">
+        <x:v>45827.1931712963</x:v>
+      </x:c>
+      <x:c r="I21" s="18">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="n">
+        <x:v>1234312</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="n">
+        <x:v>18810</x:v>
+      </x:c>
+      <x:c r="L21" s="20">
+        <x:v>45827.2195833333</x:v>
+      </x:c>
+      <x:c r="M21" s="16" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="21" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="s"/>
+      <x:c r="D24" s="22" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="23" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="24" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C25" s="25" t="s"/>
+      <x:c r="D25" s="25" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="26" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="27" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="28" t="s"/>
+      <x:c r="D26" s="28" t="s"/>
+      <x:c r="E26" s="28" t="s"/>
+      <x:c r="F26" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="27" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="s"/>
+      <x:c r="D27" s="28" t="s"/>
+      <x:c r="E27" s="28" t="s"/>
+      <x:c r="F27" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="27" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="s"/>
+      <x:c r="D28" s="28" t="s"/>
+      <x:c r="E28" s="28" t="s"/>
+      <x:c r="F28" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="27" t="s">
         <x:v>36</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s"/>
-      <x:c r="E12" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L12" s="18">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s"/>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="27" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L13" s="18">
-        <x:v>45827.2985763889</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s"/>
-      <x:c r="E14" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45825.2509606481</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>2744256</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L14" s="18">
-        <x:v>45825.8750462963</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="C30" s="28" t="s"/>
+      <x:c r="D30" s="28" t="s"/>
+      <x:c r="E30" s="28" t="s"/>
+      <x:c r="F30" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="27" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L15" s="18">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s"/>
-      <x:c r="E16" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K16" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L16" s="18">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="C31" s="28" t="s"/>
+      <x:c r="D31" s="28" t="s"/>
+      <x:c r="E31" s="28" t="s"/>
+      <x:c r="F31" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="27" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s"/>
-      <x:c r="E17" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K17" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L17" s="18">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
+      <x:c r="C32" s="28" t="s"/>
+      <x:c r="D32" s="28" t="s"/>
+      <x:c r="E32" s="28" t="s"/>
+      <x:c r="F32" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="27" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="s"/>
-      <x:c r="E18" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L18" s="18">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
+      <x:c r="C33" s="28" t="s"/>
+      <x:c r="D33" s="28" t="s"/>
+      <x:c r="E33" s="28" t="s"/>
+      <x:c r="F33" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="27" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s"/>
-      <x:c r="E19" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L19" s="18">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L20" s="18">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="C34" s="28" t="s"/>
+      <x:c r="D34" s="28" t="s"/>
+      <x:c r="E34" s="28" t="s"/>
+      <x:c r="F34" s="29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B35" s="30" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L21" s="18">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L22" s="18">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>45827.1931712963</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>44197</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1234312</x:v>
-      </x:c>
-      <x:c r="K23" s="17" t="n">
-        <x:v>18810</x:v>
-      </x:c>
-      <x:c r="L23" s="18">
-        <x:v>45827.2195833333</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="19" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="C26" s="20" t="s"/>
-      <x:c r="D26" s="20" t="s"/>
-      <x:c r="E26" s="21" t="s"/>
-      <x:c r="F26" s="21" t="s"/>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="24" t="s">
-        <x:v>85</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="25" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C30" s="26" t="s"/>
-      <x:c r="D30" s="26" t="s"/>
-      <x:c r="E30" s="26" t="s"/>
-      <x:c r="F30" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="25" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C32" s="26" t="s"/>
-      <x:c r="D32" s="26" t="s"/>
-      <x:c r="E32" s="26" t="s"/>
-      <x:c r="F32" s="27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="25" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C33" s="26" t="s"/>
-      <x:c r="D33" s="26" t="s"/>
-      <x:c r="E33" s="26" t="s"/>
-      <x:c r="F33" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="25" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C34" s="26" t="s"/>
-      <x:c r="D34" s="26" t="s"/>
-      <x:c r="E34" s="26" t="s"/>
-      <x:c r="F34" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="25" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C35" s="26" t="s"/>
-      <x:c r="D35" s="26" t="s"/>
-      <x:c r="E35" s="26" t="s"/>
-      <x:c r="F35" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="25" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C36" s="26" t="s"/>
-      <x:c r="D36" s="26" t="s"/>
-      <x:c r="E36" s="26" t="s"/>
-      <x:c r="F36" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="28" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C37" s="29" t="s"/>
-      <x:c r="D37" s="29" t="s"/>
-      <x:c r="E37" s="29" t="s"/>
-      <x:c r="F37" s="30" t="n">
+      <x:c r="C35" s="31" t="s"/>
+      <x:c r="D35" s="31" t="s"/>
+      <x:c r="E35" s="31" t="s"/>
+      <x:c r="F35" s="32" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2814,7 +2746,9 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B26:F26"/>
+    <x:mergeCell ref="B24:F24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
@@ -2824,8 +2758,6 @@
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -81,6 +81,9 @@
     <x:t>61-6-2025-1061</x:t>
   </x:si>
   <x:si>
+    <x:t>16854</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier3 edge</x:t>
   </x:si>
   <x:si>
@@ -96,6 +99,9 @@
     <x:t>61-6-2025-1023</x:t>
   </x:si>
   <x:si>
+    <x:t>1434444</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANUELITO TOLENTINO</x:t>
   </x:si>
   <x:si>
@@ -105,6 +111,9 @@
     <x:t>61-6-2025-1003</x:t>
   </x:si>
   <x:si>
+    <x:t>1546810</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -120,6 +129,9 @@
     <x:t>61-6-2025-1055</x:t>
   </x:si>
   <x:si>
+    <x:t>1435677</x:t>
+  </x:si>
+  <x:si>
     <x:t>NEW</x:t>
   </x:si>
   <x:si>
@@ -132,6 +144,9 @@
     <x:t>61-6-2025-1006</x:t>
   </x:si>
   <x:si>
+    <x:t>2744256</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radio Station License (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -147,6 +162,9 @@
     <x:t>61-6-2025-1013</x:t>
   </x:si>
   <x:si>
+    <x:t>2734401</x:t>
+  </x:si>
+  <x:si>
     <x:t>Radiotelegraphy</x:t>
   </x:si>
   <x:si>
@@ -159,6 +177,9 @@
     <x:t>61-6-2025-1054</x:t>
   </x:si>
   <x:si>
+    <x:t>1616</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANGELICA VERGARA PANCHITO</x:t>
   </x:si>
   <x:si>
@@ -168,6 +189,9 @@
     <x:t>61-6-2025-1007</x:t>
   </x:si>
   <x:si>
+    <x:t>274001</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWARD LANCE LORILLA</x:t>
   </x:si>
   <x:si>
@@ -180,6 +204,9 @@
     <x:t>61-6-2025-1025</x:t>
   </x:si>
   <x:si>
+    <x:t>1432235</x:t>
+  </x:si>
+  <x:si>
     <x:t>Request for Blocking of IMEI and SIM of Lost/Stolen Mobile Phone</x:t>
   </x:si>
   <x:si>
@@ -195,6 +222,9 @@
     <x:t>61-6-2025-1012</x:t>
   </x:si>
   <x:si>
+    <x:t>1434267</x:t>
+  </x:si>
+  <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
   </x:si>
   <x:si>
@@ -204,6 +234,9 @@
     <x:t>61-6-2025-1005</x:t>
   </x:si>
   <x:si>
+    <x:t>15135861</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -216,6 +249,10 @@
     <x:t>61-6-2025-1050</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">
+52268</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -225,6 +262,9 @@
     <x:t>61-6-2025-1016</x:t>
   </x:si>
   <x:si>
+    <x:t>1435666</x:t>
+  </x:si>
+  <x:si>
     <x:t>PLAY STORE</x:t>
   </x:si>
   <x:si>
@@ -235,6 +275,9 @@
   </x:si>
   <x:si>
     <x:t>61-6-2025-1052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234312</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -258,7 +301,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -319,13 +362,6 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
@@ -577,7 +613,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -615,50 +651,41 @@
     <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -702,6 +729,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -713,71 +744,55 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1144,7 +1159,7 @@
       <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s"/>
+      <x:c r="D8" s="14" t="s"/>
       <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
@@ -1154,23 +1169,23 @@
       <x:c r="G8" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="14">
-        <x:v>45832.3271759259</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>45832.3271990741</x:v>
-      </x:c>
-      <x:c r="J8" s="13" t="n">
-        <x:v>16854</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="H8" s="15">
+        <x:v>45832.3271846875</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>45832.3272087963</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="14">
-        <x:v>45832.3384259259</x:v>
+      <x:c r="L8" s="17">
+        <x:v>45832.3384320023</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
@@ -1178,608 +1193,608 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45826.3053530208</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45826.3053769676</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L9" s="17">
+        <x:v>45826.311800463</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="s"/>
+      <x:c r="E10" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H10" s="15">
+        <x:v>45825.0450396991</x:v>
+      </x:c>
+      <x:c r="I10" s="15">
+        <x:v>45825.0450687153</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="K10" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L10" s="17">
+        <x:v>45825.0561645718</x:v>
+      </x:c>
+      <x:c r="M10" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="s"/>
+      <x:c r="E11" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="15">
+        <x:v>45827.2931036574</x:v>
+      </x:c>
+      <x:c r="I11" s="15">
+        <x:v>45827.2931277431</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K11" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L11" s="17">
+        <x:v>45827.298578831</x:v>
+      </x:c>
+      <x:c r="M11" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="s"/>
+      <x:c r="E12" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H12" s="15">
+        <x:v>45825.2509637269</x:v>
+      </x:c>
+      <x:c r="I12" s="15">
+        <x:v>45825.2509878357</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K12" s="16" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L12" s="17">
+        <x:v>45825.8750542361</x:v>
+      </x:c>
+      <x:c r="M12" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H13" s="15">
+        <x:v>45826.1308837384</x:v>
+      </x:c>
+      <x:c r="I13" s="15">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K13" s="16" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+      <x:c r="L13" s="17">
+        <x:v>45826.1478993634</x:v>
+      </x:c>
+      <x:c r="M13" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="s"/>
+      <x:c r="E14" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H14" s="15">
+        <x:v>45827.2810495602</x:v>
+      </x:c>
+      <x:c r="I14" s="15">
+        <x:v>45827.2810737963</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K14" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L14" s="17">
+        <x:v>45827.2917648032</x:v>
+      </x:c>
+      <x:c r="M14" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="s"/>
+      <x:c r="E15" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H15" s="15">
+        <x:v>45825.2635056481</x:v>
+      </x:c>
+      <x:c r="I15" s="15">
+        <x:v>45825.2635335069</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K15" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L15" s="17">
+        <x:v>45825.2871799306</x:v>
+      </x:c>
+      <x:c r="M15" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="s"/>
+      <x:c r="E16" s="13" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H16" s="15">
+        <x:v>45826.310926169</x:v>
+      </x:c>
+      <x:c r="I16" s="15">
+        <x:v>45826.3109462384</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K16" s="16" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L16" s="17">
+        <x:v>45826.3168925232</x:v>
+      </x:c>
+      <x:c r="M16" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="s"/>
+      <x:c r="E17" s="13" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H17" s="15">
+        <x:v>45825.5009313657</x:v>
+      </x:c>
+      <x:c r="I17" s="15">
+        <x:v>45825.5010245718</x:v>
+      </x:c>
+      <x:c r="J17" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="K17" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="17">
+        <x:v>45827.2850752315</x:v>
+      </x:c>
+      <x:c r="M17" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F9" s="13" t="s">
+      <x:c r="D18" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="14">
-        <x:v>45826.3053472222</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
-        <x:v>45826.3053703704</x:v>
-      </x:c>
-      <x:c r="J9" s="13" t="n">
-        <x:v>1434444</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L9" s="14">
-        <x:v>45826.3117939815</x:v>
-      </x:c>
-      <x:c r="M9" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="16" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s">
+      <x:c r="F18" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H18" s="15">
+        <x:v>45825.1485242593</x:v>
+      </x:c>
+      <x:c r="I18" s="15">
+        <x:v>45825.1485531713</x:v>
+      </x:c>
+      <x:c r="J18" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K18" s="16" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="L18" s="17">
+        <x:v>45825.1676413542</x:v>
+      </x:c>
+      <x:c r="M18" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D10" s="17" t="s"/>
-      <x:c r="E10" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="s">
+    </x:row>
+    <x:row r="19" spans="1:28" ht="33.597656" customHeight="1">
+      <x:c r="B19" s="13" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H19" s="15">
+        <x:v>45827.0419894213</x:v>
+      </x:c>
+      <x:c r="I19" s="15">
+        <x:v>45827.0420140278</x:v>
+      </x:c>
+      <x:c r="J19" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K19" s="16" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="17">
+        <x:v>45827.0460181713</x:v>
+      </x:c>
+      <x:c r="M19" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H20" s="15">
+        <x:v>45826.1449770949</x:v>
+      </x:c>
+      <x:c r="I20" s="15">
+        <x:v>45826</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K20" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="17">
+        <x:v>45826.2821424653</x:v>
+      </x:c>
+      <x:c r="M20" s="13" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="H10" s="18">
-        <x:v>45825.0450347222</x:v>
-      </x:c>
-      <x:c r="I10" s="18">
-        <x:v>45825.0450578704</x:v>
-      </x:c>
-      <x:c r="J10" s="17" t="n">
-        <x:v>1546810</x:v>
-      </x:c>
-      <x:c r="K10" s="19" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L10" s="20">
-        <x:v>45825.0561574074</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="16" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="s"/>
-      <x:c r="E11" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="16" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H11" s="18">
-        <x:v>45827.2931018519</x:v>
-      </x:c>
-      <x:c r="I11" s="18">
-        <x:v>45827.293125</x:v>
-      </x:c>
-      <x:c r="J11" s="17" t="n">
-        <x:v>1435677</x:v>
-      </x:c>
-      <x:c r="K11" s="19" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L11" s="20">
-        <x:v>45827.2985763889</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F12" s="16" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H12" s="18">
-        <x:v>45825.2509606481</x:v>
-      </x:c>
-      <x:c r="I12" s="18">
-        <x:v>45825.2509837963</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="n">
-        <x:v>2744256</x:v>
-      </x:c>
-      <x:c r="K12" s="19" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L12" s="20">
-        <x:v>45825.8750462963</x:v>
-      </x:c>
-      <x:c r="M12" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="16" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E13" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F13" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H13" s="18">
-        <x:v>45826.1308796296</x:v>
-      </x:c>
-      <x:c r="I13" s="18">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:v>2734401</x:v>
-      </x:c>
-      <x:c r="K13" s="19" t="n">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="L13" s="20">
-        <x:v>45826.1478935185</x:v>
-      </x:c>
-      <x:c r="M13" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C14" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="s"/>
-      <x:c r="E14" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F14" s="16" t="s">
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G14" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H14" s="18">
-        <x:v>45827.2810416667</x:v>
-      </x:c>
-      <x:c r="I14" s="18">
-        <x:v>45827.2810648148</x:v>
-      </x:c>
-      <x:c r="J14" s="17" t="n">
-        <x:v>1616</x:v>
-      </x:c>
-      <x:c r="K14" s="19" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L14" s="20">
-        <x:v>45827.2917592593</x:v>
-      </x:c>
-      <x:c r="M14" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="s"/>
-      <x:c r="E15" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H15" s="18">
-        <x:v>45825.2634953704</x:v>
-      </x:c>
-      <x:c r="I15" s="18">
-        <x:v>45825.2635300926</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="n">
-        <x:v>274001</x:v>
-      </x:c>
-      <x:c r="K15" s="19" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L15" s="20">
-        <x:v>45825.2871759259</x:v>
-      </x:c>
-      <x:c r="M15" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C16" s="16" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="s"/>
-      <x:c r="E16" s="16" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F16" s="16" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H16" s="18">
-        <x:v>45826.3109259259</x:v>
-      </x:c>
-      <x:c r="I16" s="18">
-        <x:v>45826.3109375</x:v>
-      </x:c>
-      <x:c r="J16" s="17" t="n">
-        <x:v>1432235</x:v>
-      </x:c>
-      <x:c r="K16" s="19" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L16" s="20">
-        <x:v>45826.3168865741</x:v>
-      </x:c>
-      <x:c r="M16" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="16" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C17" s="16" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D17" s="17" t="s"/>
-      <x:c r="E17" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F17" s="16" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H17" s="18">
-        <x:v>45825.5009259259</x:v>
-      </x:c>
-      <x:c r="I17" s="18">
-        <x:v>45825.5010185185</x:v>
-      </x:c>
-      <x:c r="J17" s="17" t="n">
-        <x:v>1434267</x:v>
-      </x:c>
-      <x:c r="K17" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="20">
-        <x:v>45827.2850694444</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="16" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C18" s="16" t="s">
+      <x:c r="E21" s="13" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H21" s="15">
+        <x:v>45827.193172581</x:v>
+      </x:c>
+      <x:c r="I21" s="15">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J21" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K21" s="16" t="n">
+        <x:v>18810</x:v>
+      </x:c>
+      <x:c r="L21" s="17">
+        <x:v>45827.2195876273</x:v>
+      </x:c>
+      <x:c r="M21" s="13" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E18" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F18" s="16" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G18" s="16" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H18" s="18">
-        <x:v>45825.1485185185</x:v>
-      </x:c>
-      <x:c r="I18" s="18">
-        <x:v>45825.1485416667</x:v>
-      </x:c>
-      <x:c r="J18" s="17" t="n">
-        <x:v>15135861</x:v>
-      </x:c>
-      <x:c r="K18" s="19" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="L18" s="20">
-        <x:v>45825.1676388889</x:v>
-      </x:c>
-      <x:c r="M18" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="16" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C19" s="16" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D19" s="17" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E19" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F19" s="16" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="H19" s="18">
-        <x:v>45827.0419791667</x:v>
-      </x:c>
-      <x:c r="I19" s="18">
-        <x:v>45827.0420138889</x:v>
-      </x:c>
-      <x:c r="J19" s="17" t="n">
-        <x:v>52268</x:v>
-      </x:c>
-      <x:c r="K19" s="19" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L19" s="20">
-        <x:v>45827.0460069444</x:v>
-      </x:c>
-      <x:c r="M19" s="16" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="16" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C20" s="16" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D20" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E20" s="16" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F20" s="16" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H20" s="18">
-        <x:v>45826.1449768519</x:v>
-      </x:c>
-      <x:c r="I20" s="18">
-        <x:v>45826</x:v>
-      </x:c>
-      <x:c r="J20" s="17" t="n">
-        <x:v>1435666</x:v>
-      </x:c>
-      <x:c r="K20" s="19" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L20" s="20">
-        <x:v>45826.2821412037</x:v>
-      </x:c>
-      <x:c r="M20" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="16" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C21" s="16" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D21" s="17" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E21" s="16" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F21" s="16" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H21" s="18">
-        <x:v>45827.1931712963</x:v>
-      </x:c>
-      <x:c r="I21" s="18">
-        <x:v>44197</x:v>
-      </x:c>
-      <x:c r="J21" s="17" t="n">
-        <x:v>1234312</x:v>
-      </x:c>
-      <x:c r="K21" s="19" t="n">
-        <x:v>18810</x:v>
-      </x:c>
-      <x:c r="L21" s="20">
-        <x:v>45827.2195833333</x:v>
-      </x:c>
-      <x:c r="M21" s="16" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="21" t="s">
+      <x:c r="B24" s="18" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C24" s="19" t="s"/>
+      <x:c r="D24" s="19" t="s"/>
+      <x:c r="E24" s="20" t="s"/>
+      <x:c r="F24" s="20" t="s"/>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="21" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="23" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="24" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="24" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="24" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="24" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C30" s="25" t="s"/>
+      <x:c r="D30" s="25" t="s"/>
+      <x:c r="E30" s="25" t="s"/>
+      <x:c r="F30" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="24" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C31" s="25" t="s"/>
+      <x:c r="D31" s="25" t="s"/>
+      <x:c r="E31" s="25" t="s"/>
+      <x:c r="F31" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="24" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C32" s="25" t="s"/>
+      <x:c r="D32" s="25" t="s"/>
+      <x:c r="E32" s="25" t="s"/>
+      <x:c r="F32" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="24" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C24" s="22" t="s"/>
-      <x:c r="D24" s="22" t="s"/>
-      <x:c r="E24" s="23" t="s"/>
-      <x:c r="F24" s="23" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="24" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C25" s="25" t="s"/>
-      <x:c r="D25" s="25" t="s"/>
-      <x:c r="E25" s="25" t="s"/>
-      <x:c r="F25" s="26" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="27" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C26" s="28" t="s"/>
-      <x:c r="D26" s="28" t="s"/>
-      <x:c r="E26" s="28" t="s"/>
-      <x:c r="F26" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="27" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="C33" s="25" t="s"/>
+      <x:c r="D33" s="25" t="s"/>
+      <x:c r="E33" s="25" t="s"/>
+      <x:c r="F33" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="27" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C28" s="28" t="s"/>
-      <x:c r="D28" s="28" t="s"/>
-      <x:c r="E28" s="28" t="s"/>
-      <x:c r="F28" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="27" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="27" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C30" s="28" t="s"/>
-      <x:c r="D30" s="28" t="s"/>
-      <x:c r="E30" s="28" t="s"/>
-      <x:c r="F30" s="29" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="27" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C31" s="28" t="s"/>
-      <x:c r="D31" s="28" t="s"/>
-      <x:c r="E31" s="28" t="s"/>
-      <x:c r="F31" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="27" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C32" s="28" t="s"/>
-      <x:c r="D32" s="28" t="s"/>
-      <x:c r="E32" s="28" t="s"/>
-      <x:c r="F32" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="27" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C33" s="28" t="s"/>
-      <x:c r="D33" s="28" t="s"/>
-      <x:c r="E33" s="28" t="s"/>
-      <x:c r="F33" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="27" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C34" s="28" t="s"/>
-      <x:c r="D34" s="28" t="s"/>
-      <x:c r="E34" s="28" t="s"/>
-      <x:c r="F34" s="29" t="n">
+      <x:c r="B34" s="24" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C34" s="25" t="s"/>
+      <x:c r="D34" s="25" t="s"/>
+      <x:c r="E34" s="25" t="s"/>
+      <x:c r="F34" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="30" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C35" s="31" t="s"/>
-      <x:c r="D35" s="31" t="s"/>
-      <x:c r="E35" s="31" t="s"/>
-      <x:c r="F35" s="32" t="n">
+      <x:c r="B35" s="27" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C35" s="28" t="s"/>
+      <x:c r="D35" s="28" t="s"/>
+      <x:c r="E35" s="28" t="s"/>
+      <x:c r="F35" s="29" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -1111,7 +1111,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1151,7 +1151,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
@@ -1188,7 +1188,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1224,7 +1224,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1260,7 +1260,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
         <x:v>30</x:v>
       </x:c>
@@ -1296,7 +1296,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
         <x:v>36</x:v>
       </x:c>
@@ -1332,7 +1332,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
         <x:v>41</x:v>
       </x:c>
@@ -1370,7 +1370,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
         <x:v>47</x:v>
       </x:c>
@@ -1406,7 +1406,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
         <x:v>47</x:v>
       </x:c>
@@ -1442,7 +1442,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
         <x:v>47</x:v>
       </x:c>
@@ -1478,7 +1478,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
@@ -1514,7 +1514,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="13" t="s">
         <x:v>67</x:v>
       </x:c>
@@ -1552,7 +1552,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="33.597656" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="13" t="s">
         <x:v>71</x:v>
       </x:c>
@@ -1590,7 +1590,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="13" t="s">
         <x:v>76</x:v>
       </x:c>
@@ -1628,7 +1628,7 @@
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="13" t="s">
         <x:v>76</x:v>
       </x:c>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -22,12 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>III | June 2025</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -1073,8 +1070,8 @@
     </x:row>
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="11" t="s">
-        <x:v>1</x:v>
+      <x:c r="B4" s="11">
+        <x:v>45809</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -1114,60 +1111,60 @@
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="M7" s="12" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="M7" s="12" t="s">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="13" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="D8" s="14" t="s"/>
       <x:c r="E8" s="13" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="G8" s="13" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="G8" s="13" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="H8" s="15">
         <x:v>45832.3271846875</x:v>
@@ -1176,7 +1173,7 @@
         <x:v>45832.3272087963</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>50</x:v>
@@ -1185,25 +1182,25 @@
         <x:v>45832.3384320023</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s"/>
       <x:c r="E9" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F9" s="13" t="s">
+      <x:c r="G9" s="13" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>45826.3053530208</x:v>
@@ -1212,7 +1209,7 @@
         <x:v>45826.3053769676</x:v>
       </x:c>
       <x:c r="J9" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
         <x:v>50</x:v>
@@ -1221,25 +1218,25 @@
         <x:v>45826.311800463</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D10" s="14" t="s"/>
       <x:c r="E10" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F10" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="13" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="H10" s="15">
         <x:v>45825.0450396991</x:v>
@@ -1248,7 +1245,7 @@
         <x:v>45825.0450687153</x:v>
       </x:c>
       <x:c r="J10" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
         <x:v>50</x:v>
@@ -1257,25 +1254,25 @@
         <x:v>45825.0561645718</x:v>
       </x:c>
       <x:c r="M10" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="13" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="14" t="s"/>
       <x:c r="E11" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F11" s="13" t="s">
+      <x:c r="G11" s="13" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="G11" s="13" t="s">
-        <x:v>34</x:v>
       </x:c>
       <x:c r="H11" s="15">
         <x:v>45827.2931036574</x:v>
@@ -1284,7 +1281,7 @@
         <x:v>45827.2931277431</x:v>
       </x:c>
       <x:c r="J11" s="14" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K11" s="16" t="n">
         <x:v>130</x:v>
@@ -1293,25 +1290,25 @@
         <x:v>45827.298578831</x:v>
       </x:c>
       <x:c r="M11" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="C12" s="13" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="14" t="s"/>
       <x:c r="E12" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F12" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="G12" s="13" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="H12" s="15">
         <x:v>45825.2509637269</x:v>
@@ -1320,7 +1317,7 @@
         <x:v>45825.2509878357</x:v>
       </x:c>
       <x:c r="J12" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K12" s="16" t="n">
         <x:v>4530</x:v>
@@ -1329,27 +1326,27 @@
         <x:v>45825.8750542361</x:v>
       </x:c>
       <x:c r="M12" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C13" s="13" t="s">
+      <x:c r="D13" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="s">
+      <x:c r="E13" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="E13" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F13" s="13" t="s">
+      <x:c r="G13" s="13" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="G13" s="13" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="H13" s="15">
         <x:v>45826.1308837384</x:v>
@@ -1358,7 +1355,7 @@
         <x:v>45826</x:v>
       </x:c>
       <x:c r="J13" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K13" s="16" t="n">
         <x:v>1052</x:v>
@@ -1367,25 +1364,25 @@
         <x:v>45826.1478993634</x:v>
       </x:c>
       <x:c r="M13" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="C14" s="13" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="D14" s="14" t="s"/>
       <x:c r="E14" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F14" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="G14" s="13" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="H14" s="15">
         <x:v>45827.2810495602</x:v>
@@ -1394,7 +1391,7 @@
         <x:v>45827.2810737963</x:v>
       </x:c>
       <x:c r="J14" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K14" s="16" t="n">
         <x:v>50</x:v>
@@ -1403,25 +1400,25 @@
         <x:v>45827.2917648032</x:v>
       </x:c>
       <x:c r="M14" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C15" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D15" s="14" t="s"/>
       <x:c r="E15" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F15" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G15" s="13" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H15" s="15">
         <x:v>45825.2635056481</x:v>
@@ -1430,7 +1427,7 @@
         <x:v>45825.2635335069</x:v>
       </x:c>
       <x:c r="J15" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K15" s="16" t="n">
         <x:v>50</x:v>
@@ -1439,25 +1436,25 @@
         <x:v>45825.2871799306</x:v>
       </x:c>
       <x:c r="M15" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C16" s="13" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D16" s="14" t="s"/>
       <x:c r="E16" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F16" s="13" t="s">
+      <x:c r="G16" s="13" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="G16" s="13" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="H16" s="15">
         <x:v>45826.310926169</x:v>
@@ -1466,7 +1463,7 @@
         <x:v>45826.3109462384</x:v>
       </x:c>
       <x:c r="J16" s="14" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K16" s="16" t="n">
         <x:v>50</x:v>
@@ -1475,25 +1472,25 @@
         <x:v>45826.3168925232</x:v>
       </x:c>
       <x:c r="M16" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="13" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="C17" s="13" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="D17" s="14" t="s"/>
       <x:c r="E17" s="13" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F17" s="13" t="s">
+      <x:c r="G17" s="13" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="G17" s="13" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="H17" s="15">
         <x:v>45825.5009313657</x:v>
@@ -1502,7 +1499,7 @@
         <x:v>45825.5010245718</x:v>
       </x:c>
       <x:c r="J17" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K17" s="16" t="n">
         <x:v>0</x:v>
@@ -1511,27 +1508,27 @@
         <x:v>45827.2850752315</x:v>
       </x:c>
       <x:c r="M17" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="13" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C18" s="13" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D18" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E18" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F18" s="13" t="s">
+      <x:c r="G18" s="13" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="G18" s="13" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="15">
         <x:v>45825.1485242593</x:v>
@@ -1540,7 +1537,7 @@
         <x:v>45825.1485531713</x:v>
       </x:c>
       <x:c r="J18" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K18" s="16" t="n">
         <x:v>360</x:v>
@@ -1549,27 +1546,27 @@
         <x:v>45825.1676413542</x:v>
       </x:c>
       <x:c r="M18" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C19" s="13" t="s">
+      <x:c r="D19" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D19" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E19" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F19" s="13" t="s">
+      <x:c r="G19" s="13" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="G19" s="13" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="H19" s="15">
         <x:v>45827.0419894213</x:v>
@@ -1578,7 +1575,7 @@
         <x:v>45827.0420140278</x:v>
       </x:c>
       <x:c r="J19" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K19" s="16" t="n">
         <x:v>3530</x:v>
@@ -1587,27 +1584,27 @@
         <x:v>45827.0460181713</x:v>
       </x:c>
       <x:c r="M19" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C20" s="13" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D20" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E20" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F20" s="13" t="s">
+      <x:c r="G20" s="13" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="G20" s="13" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="H20" s="15">
         <x:v>45826.1449770949</x:v>
@@ -1616,7 +1613,7 @@
         <x:v>45826</x:v>
       </x:c>
       <x:c r="J20" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K20" s="16" t="n">
         <x:v>3030</x:v>
@@ -1625,27 +1622,27 @@
         <x:v>45826.2821424653</x:v>
       </x:c>
       <x:c r="M20" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="13" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C21" s="13" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D21" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E21" s="13" t="s">
+      <x:c r="F21" s="13" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="F21" s="13" t="s">
+      <x:c r="G21" s="13" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="G21" s="13" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="15">
         <x:v>45827.193172581</x:v>
@@ -1654,7 +1651,7 @@
         <x:v>44197</x:v>
       </x:c>
       <x:c r="J21" s="14" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K21" s="16" t="n">
         <x:v>18810</x:v>
@@ -1663,14 +1660,14 @@
         <x:v>45827.2195876273</x:v>
       </x:c>
       <x:c r="M21" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="18" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C24" s="19" t="s"/>
       <x:c r="D24" s="19" t="s"/>
@@ -1679,18 +1676,18 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="22" customHeight="1">
       <x:c r="B25" s="21" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C25" s="22" t="s"/>
       <x:c r="D25" s="22" t="s"/>
       <x:c r="E25" s="22" t="s"/>
       <x:c r="F25" s="23" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C26" s="25" t="s"/>
       <x:c r="D26" s="25" t="s"/>
@@ -1701,7 +1698,7 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="24" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C27" s="25" t="s"/>
       <x:c r="D27" s="25" t="s"/>
@@ -1712,7 +1709,7 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
       <x:c r="B28" s="24" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C28" s="25" t="s"/>
       <x:c r="D28" s="25" t="s"/>
@@ -1723,7 +1720,7 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="24" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="25" t="s"/>
       <x:c r="D29" s="25" t="s"/>
@@ -1734,7 +1731,7 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="24" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C30" s="25" t="s"/>
       <x:c r="D30" s="25" t="s"/>
@@ -1745,7 +1742,7 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="24" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C31" s="25" t="s"/>
       <x:c r="D31" s="25" t="s"/>
@@ -1756,7 +1753,7 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="24" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C32" s="25" t="s"/>
       <x:c r="D32" s="25" t="s"/>
@@ -1767,7 +1764,7 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="24" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C33" s="25" t="s"/>
       <x:c r="D33" s="25" t="s"/>
@@ -1778,7 +1775,7 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="24" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C34" s="25" t="s"/>
       <x:c r="D34" s="25" t="s"/>
@@ -1789,7 +1786,7 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
       <x:c r="B35" s="27" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C35" s="28" t="s"/>
       <x:c r="D35" s="28" t="s"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -344,7 +344,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -610,7 +610,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -621,7 +621,10 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -682,7 +685,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -717,7 +720,11 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1073,17 +1080,17 @@
       <x:c r="B4" s="11">
         <x:v>45809</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="s"/>
-      <x:c r="D4" s="11" t="s"/>
-      <x:c r="E4" s="11" t="s"/>
-      <x:c r="F4" s="11" t="s"/>
-      <x:c r="G4" s="11" t="s"/>
-      <x:c r="H4" s="11" t="s"/>
-      <x:c r="I4" s="11" t="s"/>
-      <x:c r="J4" s="11" t="s"/>
-      <x:c r="K4" s="11" t="s"/>
-      <x:c r="L4" s="11" t="s"/>
-      <x:c r="M4" s="11" t="s"/>
+      <x:c r="C4" s="12" t="s"/>
+      <x:c r="D4" s="12" t="s"/>
+      <x:c r="E4" s="12" t="s"/>
+      <x:c r="F4" s="12" t="s"/>
+      <x:c r="G4" s="12" t="s"/>
+      <x:c r="H4" s="12" t="s"/>
+      <x:c r="I4" s="12" t="s"/>
+      <x:c r="J4" s="12" t="s"/>
+      <x:c r="K4" s="12" t="s"/>
+      <x:c r="L4" s="12" t="s"/>
+      <x:c r="M4" s="12" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -1110,688 +1117,688 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="12" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="12" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="16">
         <x:v>45832.3271846875</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I8" s="16">
         <x:v>45832.3272087963</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L8" s="17">
+      <x:c r="L8" s="18">
         <x:v>45832.3384320023</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="13" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="13" t="s">
+      <x:c r="D9" s="15" t="s"/>
+      <x:c r="E9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F9" s="13" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="G9" s="13" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="H9" s="15">
+      <x:c r="H9" s="16">
         <x:v>45826.3053530208</x:v>
       </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="I9" s="16">
         <x:v>45826.3053769676</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L9" s="17">
+      <x:c r="L9" s="18">
         <x:v>45826.311800463</x:v>
       </x:c>
-      <x:c r="M9" s="13" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="13" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C10" s="13" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="s"/>
-      <x:c r="E10" s="13" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F10" s="13" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G10" s="13" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="H10" s="15">
+      <x:c r="H10" s="16">
         <x:v>45825.0450396991</x:v>
       </x:c>
-      <x:c r="I10" s="15">
+      <x:c r="I10" s="16">
         <x:v>45825.0450687153</x:v>
       </x:c>
-      <x:c r="J10" s="14" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K10" s="16" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L10" s="17">
+      <x:c r="L10" s="18">
         <x:v>45825.0561645718</x:v>
       </x:c>
-      <x:c r="M10" s="13" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="13" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C11" s="13" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="s"/>
-      <x:c r="E11" s="13" t="s">
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="F11" s="13" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G11" s="13" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="H11" s="15">
+      <x:c r="H11" s="16">
         <x:v>45827.2931036574</x:v>
       </x:c>
-      <x:c r="I11" s="15">
+      <x:c r="I11" s="16">
         <x:v>45827.2931277431</x:v>
       </x:c>
-      <x:c r="J11" s="14" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K11" s="16" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L11" s="17">
+      <x:c r="L11" s="18">
         <x:v>45827.298578831</x:v>
       </x:c>
-      <x:c r="M11" s="13" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="13" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C12" s="13" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D12" s="14" t="s"/>
-      <x:c r="E12" s="13" t="s">
+      <x:c r="D12" s="15" t="s"/>
+      <x:c r="E12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F12" s="13" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G12" s="13" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H12" s="15">
+      <x:c r="H12" s="16">
         <x:v>45825.2509637269</x:v>
       </x:c>
-      <x:c r="I12" s="15">
+      <x:c r="I12" s="16">
         <x:v>45825.2509878357</x:v>
       </x:c>
-      <x:c r="J12" s="14" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K12" s="16" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L12" s="17">
+      <x:c r="L12" s="18">
         <x:v>45825.8750542361</x:v>
       </x:c>
-      <x:c r="M12" s="13" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="13" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C13" s="13" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E13" s="13" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F13" s="13" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G13" s="13" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H13" s="15">
+      <x:c r="H13" s="16">
         <x:v>45826.1308837384</x:v>
       </x:c>
-      <x:c r="I13" s="15">
+      <x:c r="I13" s="16">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J13" s="14" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K13" s="16" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1052</x:v>
       </x:c>
-      <x:c r="L13" s="17">
+      <x:c r="L13" s="18">
         <x:v>45826.1478993634</x:v>
       </x:c>
-      <x:c r="M13" s="13" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="13" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C14" s="13" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="s"/>
-      <x:c r="E14" s="13" t="s">
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F14" s="13" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G14" s="13" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H14" s="15">
+      <x:c r="H14" s="16">
         <x:v>45827.2810495602</x:v>
       </x:c>
-      <x:c r="I14" s="15">
+      <x:c r="I14" s="16">
         <x:v>45827.2810737963</x:v>
       </x:c>
-      <x:c r="J14" s="14" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K14" s="16" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L14" s="17">
+      <x:c r="L14" s="18">
         <x:v>45827.2917648032</x:v>
       </x:c>
-      <x:c r="M14" s="13" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="13" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C15" s="13" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="D15" s="14" t="s"/>
-      <x:c r="E15" s="13" t="s">
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H15" s="15">
+      <x:c r="H15" s="16">
         <x:v>45825.2635056481</x:v>
       </x:c>
-      <x:c r="I15" s="15">
+      <x:c r="I15" s="16">
         <x:v>45825.2635335069</x:v>
       </x:c>
-      <x:c r="J15" s="14" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="K15" s="16" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L15" s="17">
+      <x:c r="L15" s="18">
         <x:v>45825.2871799306</x:v>
       </x:c>
-      <x:c r="M15" s="13" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="13" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C16" s="13" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D16" s="14" t="s"/>
-      <x:c r="E16" s="13" t="s">
+      <x:c r="D16" s="15" t="s"/>
+      <x:c r="E16" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F16" s="13" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G16" s="13" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H16" s="15">
+      <x:c r="H16" s="16">
         <x:v>45826.310926169</x:v>
       </x:c>
-      <x:c r="I16" s="15">
+      <x:c r="I16" s="16">
         <x:v>45826.3109462384</x:v>
       </x:c>
-      <x:c r="J16" s="14" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K16" s="16" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="L16" s="17">
+      <x:c r="L16" s="18">
         <x:v>45826.3168925232</x:v>
       </x:c>
-      <x:c r="M16" s="13" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="13" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C17" s="13" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D17" s="14" t="s"/>
-      <x:c r="E17" s="13" t="s">
+      <x:c r="D17" s="15" t="s"/>
+      <x:c r="E17" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F17" s="13" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G17" s="13" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H17" s="15">
+      <x:c r="H17" s="16">
         <x:v>45825.5009313657</x:v>
       </x:c>
-      <x:c r="I17" s="15">
+      <x:c r="I17" s="16">
         <x:v>45825.5010245718</x:v>
       </x:c>
-      <x:c r="J17" s="14" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="K17" s="16" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="17">
+      <x:c r="L17" s="18">
         <x:v>45827.2850752315</x:v>
       </x:c>
-      <x:c r="M17" s="13" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="13" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C18" s="13" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D18" s="14" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E18" s="13" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F18" s="13" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G18" s="13" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H18" s="15">
+      <x:c r="H18" s="16">
         <x:v>45825.1485242593</x:v>
       </x:c>
-      <x:c r="I18" s="15">
+      <x:c r="I18" s="16">
         <x:v>45825.1485531713</x:v>
       </x:c>
-      <x:c r="J18" s="14" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="K18" s="16" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="L18" s="17">
+      <x:c r="L18" s="18">
         <x:v>45825.1676413542</x:v>
       </x:c>
-      <x:c r="M18" s="13" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="13" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C19" s="13" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D19" s="14" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E19" s="13" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F19" s="13" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G19" s="13" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H19" s="15">
+      <x:c r="H19" s="16">
         <x:v>45827.0419894213</x:v>
       </x:c>
-      <x:c r="I19" s="15">
+      <x:c r="I19" s="16">
         <x:v>45827.0420140278</x:v>
       </x:c>
-      <x:c r="J19" s="14" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="K19" s="16" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L19" s="17">
+      <x:c r="L19" s="18">
         <x:v>45827.0460181713</x:v>
       </x:c>
-      <x:c r="M19" s="13" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="13" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C20" s="13" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D20" s="14" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E20" s="13" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F20" s="13" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G20" s="13" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="H20" s="15">
+      <x:c r="H20" s="16">
         <x:v>45826.1449770949</x:v>
       </x:c>
-      <x:c r="I20" s="15">
+      <x:c r="I20" s="16">
         <x:v>45826</x:v>
       </x:c>
-      <x:c r="J20" s="14" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="K20" s="16" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L20" s="17">
+      <x:c r="L20" s="18">
         <x:v>45826.2821424653</x:v>
       </x:c>
-      <x:c r="M20" s="13" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="13" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C21" s="13" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D21" s="14" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E21" s="13" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="F21" s="13" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G21" s="13" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H21" s="15">
+      <x:c r="H21" s="16">
         <x:v>45827.193172581</x:v>
       </x:c>
-      <x:c r="I21" s="15">
+      <x:c r="I21" s="16">
         <x:v>44197</x:v>
       </x:c>
-      <x:c r="J21" s="14" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="K21" s="16" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>18810</x:v>
       </x:c>
-      <x:c r="L21" s="17">
+      <x:c r="L21" s="18">
         <x:v>45827.2195876273</x:v>
       </x:c>
-      <x:c r="M21" s="13" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="18" t="s">
+      <x:c r="B24" s="19" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C24" s="19" t="s"/>
-      <x:c r="D24" s="19" t="s"/>
-      <x:c r="E24" s="20" t="s"/>
-      <x:c r="F24" s="20" t="s"/>
+      <x:c r="C24" s="20" t="s"/>
+      <x:c r="D24" s="20" t="s"/>
+      <x:c r="E24" s="21" t="s"/>
+      <x:c r="F24" s="21" t="s"/>
     </x:row>
     <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="21" t="s">
+      <x:c r="B25" s="22" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="23" t="s">
+      <x:c r="C25" s="23" t="s"/>
+      <x:c r="D25" s="23" t="s"/>
+      <x:c r="E25" s="23" t="s"/>
+      <x:c r="F25" s="24" t="s">
         <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="24" t="s">
+      <x:c r="B26" s="25" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C26" s="25" t="s"/>
-      <x:c r="D26" s="25" t="s"/>
-      <x:c r="E26" s="25" t="s"/>
-      <x:c r="F26" s="26" t="n">
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="24" t="s">
+      <x:c r="B27" s="25" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="26" t="n">
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="24" t="s">
+      <x:c r="B28" s="25" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C28" s="25" t="s"/>
-      <x:c r="D28" s="25" t="s"/>
-      <x:c r="E28" s="25" t="s"/>
-      <x:c r="F28" s="26" t="n">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="24" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C29" s="25" t="s"/>
-      <x:c r="D29" s="25" t="s"/>
-      <x:c r="E29" s="25" t="s"/>
-      <x:c r="F29" s="26" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="24" t="s">
+      <x:c r="B30" s="25" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C30" s="25" t="s"/>
-      <x:c r="D30" s="25" t="s"/>
-      <x:c r="E30" s="25" t="s"/>
-      <x:c r="F30" s="26" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="24" t="s">
+      <x:c r="B31" s="25" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C31" s="25" t="s"/>
-      <x:c r="D31" s="25" t="s"/>
-      <x:c r="E31" s="25" t="s"/>
-      <x:c r="F31" s="26" t="n">
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="24" t="s">
+      <x:c r="B32" s="25" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C32" s="25" t="s"/>
-      <x:c r="D32" s="25" t="s"/>
-      <x:c r="E32" s="25" t="s"/>
-      <x:c r="F32" s="26" t="n">
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="24" t="s">
+      <x:c r="B33" s="25" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C33" s="25" t="s"/>
-      <x:c r="D33" s="25" t="s"/>
-      <x:c r="E33" s="25" t="s"/>
-      <x:c r="F33" s="26" t="n">
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="24" t="s">
+      <x:c r="B34" s="25" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="C34" s="25" t="s"/>
-      <x:c r="D34" s="25" t="s"/>
-      <x:c r="E34" s="25" t="s"/>
-      <x:c r="F34" s="26" t="n">
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="27" t="s">
+      <x:c r="B35" s="28" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C35" s="28" t="s"/>
-      <x:c r="D35" s="28" t="s"/>
-      <x:c r="E35" s="28" t="s"/>
-      <x:c r="F35" s="29" t="n">
+      <x:c r="C35" s="29" t="s"/>
+      <x:c r="D35" s="29" t="s"/>
+      <x:c r="E35" s="29" t="s"/>
+      <x:c r="F35" s="30" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-III-202501-202612.xlsx.xlsx
@@ -66,28 +66,97 @@
     <x:t>Amateur</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA ABASTAS AMANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manimpis, City Of San Fernando (Capital), Pampanga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1023-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1061</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16854</x:t>
+    <x:t>JULIETA ROBLEDO AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1003-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1546810</x:t>
   </x:si>
   <x:si>
     <x:t>cashier3 edge</x:t>
   </x:si>
   <x:si>
-    <x:t>JULIETA ROBLEDO AMANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Maimpis, City Of San Fernando (Capital), Pampanga</x:t>
+    <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RROC-RLM-ROIII-1005-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15135861</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radiotelegraphy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGELICA VERGARA PANCHITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1007-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>274001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANUELITO TOLENTINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW CORP INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CPE-ROIII-1006-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2744256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Station License (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JUAN DELA CRUZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RSL-ROIII-1002-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2734401</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MP-ROIII-1003-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1435666</x:t>
   </x:si>
   <x:si>
     <x:t>TEMP-ROIII-1018-25</x:t>
@@ -99,96 +168,6 @@
     <x:t>1434444</x:t>
   </x:si>
   <x:si>
-    <x:t>MANUELITO TOLENTINO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1003-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1546810</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALEX C. LAGUISMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50-30 B Dña Isabel Avenue, Pulung Maragul, Angeles City, Pampanga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AT-RSL-ROIII-1022-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1435677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEW CORP INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CPE-ROIII-1006-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2744256</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Radio Station License (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JUAN DELA CRUZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RSL-ROIII-1002-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2734401</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Radiotelegraphy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEL PANCHITO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1021-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1054</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1616</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGELICA VERGARA PANCHITO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1007-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>274001</x:t>
-  </x:si>
-  <x:si>
     <x:t>EDWARD LANCE LORILLA</x:t>
   </x:si>
   <x:si>
@@ -202,36 +181,6 @@
   </x:si>
   <x:si>
     <x:t>1432235</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Request for Blocking of IMEI and SIM of Lost/Stolen Mobile Phone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JOHN ANTHONY AUSTRIA ROXAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30 bot 1 District 3, Pulong cacutud, Angeles City, Pampanga</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEMP-ROIII-1011-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1434267</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RROC-RLM-ROIII-1005-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15135861</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (NEW)</x:t>
@@ -250,18 +199,6 @@
 52268</x:t>
   </x:si>
   <x:si>
-    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MP-ROIII-1003-25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-6-2025-1016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1435666</x:t>
-  </x:si>
-  <x:si>
     <x:t>PLAY STORE</x:t>
   </x:si>
   <x:si>
@@ -275,6 +212,69 @@
   </x:si>
   <x:si>
     <x:t>1234312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Request for Blocking of IMEI and SIM of Lost/Stolen Mobile Phone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOHN ANTHONY AUSTRIA ROXAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30 bot 1 District 3, Pulong cacutud, Angeles City, Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1011-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1434267</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEL PANCHITO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1021-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1054</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1616</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALEX C. LAGUISMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50-30 B Dña Isabel Avenue, Pulung Maragul, Angeles City, Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AT-RSL-ROIII-1022-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1435677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manimpis, City Of San Fernando (Capital), Pampanga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIII-1023-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-6-2025-1061</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16854</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1174,10 +1174,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>45832.3271846875</x:v>
+        <x:v>45825.0450396991</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>45832.3272087963</x:v>
+        <x:v>45825.0450687153</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>18</x:v>
@@ -1186,7 +1186,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>45832.3384320023</x:v>
+        <x:v>45825.0561645718</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>19</x:v>
@@ -1194,14 +1194,16 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
         <x:v>22</x:v>
@@ -1210,70 +1212,70 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>45826.3053530208</x:v>
+        <x:v>45825.1485242593</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>45826.3053769676</x:v>
+        <x:v>45825.1485531713</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>50</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>45826.311800463</x:v>
+        <x:v>45825.1676413542</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s"/>
       <x:c r="E10" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>45825.0450396991</x:v>
+        <x:v>45825.2635056481</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>45825.0450687153</x:v>
+        <x:v>45825.2635335069</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>45825.0561645718</x:v>
+        <x:v>45825.2871799306</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s"/>
       <x:c r="E11" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
         <x:v>32</x:v>
@@ -1282,22 +1284,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>45827.2931036574</x:v>
+        <x:v>45825.2509637269</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>45827.2931277431</x:v>
+        <x:v>45825.2509878357</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>130</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>45827.298578831</x:v>
+        <x:v>45825.8750542361</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
@@ -1307,288 +1309,290 @@
       <x:c r="C12" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="s"/>
+      <x:c r="D12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>45825.2509637269</x:v>
+        <x:v>45826.1308837384</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>45825.2509878357</x:v>
+        <x:v>45826</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>4530</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>45825.8750542361</x:v>
+        <x:v>45826.1478993634</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="H13" s="16">
-        <x:v>45826.1308837384</x:v>
+        <x:v>45826.1449770949</x:v>
       </x:c>
       <x:c r="I13" s="16">
         <x:v>45826</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>1052</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>45826.1478993634</x:v>
+        <x:v>45826.2821424653</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s"/>
       <x:c r="E14" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>45827.2810495602</x:v>
+        <x:v>45826.3053530208</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>45827.2810737963</x:v>
+        <x:v>45826.3053769676</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>45827.2917648032</x:v>
+        <x:v>45826.311800463</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s"/>
       <x:c r="E15" s="14" t="s">
-        <x:v>21</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45826.310926169</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>45826.3109462384</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45825.2635056481</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>45825.2635335069</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>45825.2871799306</x:v>
+        <x:v>45826.3168925232</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s"/>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>45827.0419894213</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>45827.0420140278</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>45826.310926169</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>45826.3109462384</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>50</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>45826.3168925232</x:v>
+        <x:v>45827.0460181713</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s"/>
-      <x:c r="E17" s="14" t="s">
+      <x:c r="H17" s="16">
+        <x:v>45827.193172581</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>44197</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>45825.5009313657</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>45825.5010245718</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>18810</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>45827.2850752315</x:v>
+        <x:v>45827.2195876273</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s"/>
+      <x:c r="E18" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="H18" s="16">
+        <x:v>45825.5009313657</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>45825.5010245718</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="H18" s="16">
-        <x:v>45825.1485242593</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>45825.1485531713</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>360</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>45825.1676413542</x:v>
+        <x:v>45827.2850752315</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s"/>
+      <x:c r="E19" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C19" s="14" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="H19" s="16">
+        <x:v>45827.2810495602</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>45827.2810737963</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>45827.0419894213</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>45827.0420140278</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>45827.0460181713</x:v>
+        <x:v>45827.2917648032</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>19</x:v>
@@ -1596,16 +1600,14 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s"/>
+      <x:c r="E20" s="14" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
         <x:v>76</x:v>
@@ -1614,34 +1616,32 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>45826.1449770949</x:v>
+        <x:v>45827.2931036574</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>45826</x:v>
+        <x:v>45827.2931277431</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>45826.2821424653</x:v>
+        <x:v>45827.298578831</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
+      <x:c r="D21" s="15" t="s"/>
       <x:c r="E21" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
@@ -1652,19 +1652,19 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>45827.193172581</x:v>
+        <x:v>45832.3271846875</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>44197</x:v>
+        <x:v>45832.3272087963</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>18810</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>45827.2195876273</x:v>
+        <x:v>45832.3384320023</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>19</x:v>
@@ -1705,7 +1705,7 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="25" t="s">
-        <x:v>29</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C27" s="26" t="s"/>
       <x:c r="D27" s="26" t="s"/>
@@ -1716,7 +1716,7 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
       <x:c r="B28" s="25" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C28" s="26" t="s"/>
       <x:c r="D28" s="26" t="s"/>
@@ -1727,7 +1727,7 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="25" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C29" s="26" t="s"/>
       <x:c r="D29" s="26" t="s"/>
@@ -1738,7 +1738,7 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="25" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C30" s="26" t="s"/>
       <x:c r="D30" s="26" t="s"/>
@@ -1749,7 +1749,7 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="25" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C31" s="26" t="s"/>
       <x:c r="D31" s="26" t="s"/>
@@ -1760,7 +1760,7 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="25" t="s">
-        <x:v>66</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C32" s="26" t="s"/>
       <x:c r="D32" s="26" t="s"/>
@@ -1771,7 +1771,7 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="25" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C33" s="26" t="s"/>
       <x:c r="D33" s="26" t="s"/>
@@ -1782,7 +1782,7 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="25" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C34" s="26" t="s"/>
       <x:c r="D34" s="26" t="s"/>
